--- a/input/mapping/030. OCB_GOLD_TCKH_V_T24_CRB_FULLLIST_PHAT.xlsx
+++ b/input/mapping/030. OCB_GOLD_TCKH_V_T24_CRB_FULLLIST_PHAT.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30408"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rafflescomvn.sharepoint.com/sites/OCBDataBricks-02.VngCTableau/Shared Documents/01. KHTC - Phân tích/06. Mapping View Layer 1/01.REVIEWED__OK/MAPPING_GOLD_BATCH_01_20260714/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1159" documentId="13_ncr:1_{41AF731F-2010-41DC-BF12-24D975B98159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8541EBD-9FEB-40EE-B8F3-B5411830DCF8}"/>
+  <xr:revisionPtr revIDLastSave="1206" documentId="13_ncr:1_{41AF731F-2010-41DC-BF12-24D975B98159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38219142-0389-42EE-B993-F301FADC00BD}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="9" r:id="rId1"/>
     <sheet name="Script" sheetId="10" r:id="rId2"/>
-    <sheet name="HOLIDAY" sheetId="15" r:id="rId3"/>
-    <sheet name="V_T24_CRB_FULLLIST" sheetId="5" r:id="rId4"/>
-    <sheet name="WORKING_DAY" sheetId="16" r:id="rId5"/>
+    <sheet name="V_T24_CRB_FULLLIST" sheetId="5" r:id="rId3"/>
+    <sheet name="T24_CRB" sheetId="6" r:id="rId4"/>
+    <sheet name="T24_CUSTOMER" sheetId="11" r:id="rId5"/>
     <sheet name="BRANCH_LIST" sheetId="18" r:id="rId6"/>
     <sheet name="CB_OU_DIM" sheetId="19" r:id="rId7"/>
-    <sheet name="T24_CRB" sheetId="6" r:id="rId8"/>
-    <sheet name="T24_CUSTOMER" sheetId="11" r:id="rId9"/>
+    <sheet name="WORKING_DAY" sheetId="16" r:id="rId8"/>
+    <sheet name="HOLIDAY" sheetId="15" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -393,63 +393,12 @@
     <t>Code mới</t>
   </si>
   <si>
-    <t xml:space="preserve">USE CATALOG IDENTIFIER(:curated);
+    <t>USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tckh;
-CREATE TABLE IF NOT EXISTS T24_CUSTOMER (
-    IP_ID                   INT,
-    ID                      DECIMAL(10, 0),
-    DATA_DATE               STRING,
-    T_SHORT_NAME            STRING,
-    T_LANGUAGE              STRING,
-    T_CREATE_DATE           STRING,
-    T_EDUCATION_LEVEL       STRING,
-    T_JOB_TITLE             STRING,
-    T_OCCUPATION            STRING,
-    T_MARITAL_STATUS        STRING,
-    T_LABOUR_NUMBER         DECIMAL(6, 0),
-    T_GENDER                STRING,
-    T_BIRTH_INCORP_DATE     STRING,
-    T_RESIDENCE             STRING,
-    T_NATIONALITY           STRING,
-    T_ADDRESS               STRING,
-    T_TOWN_COUNTRY          STRING,
-    T_PROVINCE_1            STRING,
-    T_PHONE_1               STRING,
-    T_SMS_1                 STRING,
-    T_OFF_PHONE             STRING,
-    T_EMAIL_1               STRING,
-    T_PROVINCE_2            STRING,
-    T_TOWN_COUNTRY_2        STRING,
-    T_SMS_2                 STRING,
-    T_PHONE_2               STRING,
-    T_OFF_PHONE_2           STRING,
-    T_SECTOR                DECIMAL(4, 0),
-    T_INDUSTRY              DECIMAL(4, 0),
-    T_CUST_GROUP            STRING,
-    T_TAX_ID                STRING,
-    T_LEGAL_ID              STRING,
-    T_LEGAL_DOC_NAME        STRING,
-    T_CONTACT_DATE          STRING,
-    T_PROVINCE              DECIMAL(4, 0),
-    T_FAX_1                 STRING,
-    T_EMAIL_2               STRING,
-    T_NET_MONTHLY_IN        DECIMAL(20, 4),
-    T_TOTAL_PROPERTY        STRING,
-    T_TOTAL_INCOME          STRING,
-    T_COMPANY_BOOK          STRING,
-    T_ACCOUNT_OFFICER       DECIMAL(8, 0)
-)
-USING DELTA;
--- STEP 1: Xóa dữ liệu cũ theo ngày
--- -------------------------------------------------------
 DELETE FROM T24_CUSTOMER
 WHERE DATA_DATE = :DATADT;
--- -------------------------------------------------------
--- STEP 2: Nạp dữ liệu mới từ Raw Vault
--- -------------------------------------------------------
 INSERT INTO T24_CUSTOMER
 WITH
--- STS HUB: chỉ giữ key có trạng thái MỚI NHẤT (&lt;= :DATADT) = 'D'
 cust_sts_del AS (
     SELECT customer_hashkey
     FROM IDENTIFIER(:cleaned || '.raw_vault.sts_hub_customer')
@@ -457,7 +406,6 @@
     GROUP BY customer_hashkey
     HAVING max_by(cdc_status, source_event_date) = 'D'
 ),
--- HUB active: hub CUSTOMER đã LOẠI key bị xóa (anti-join cust_sts_del)
 cust_active AS (
     SELECT
         h.customer_hashkey,
@@ -469,7 +417,6 @@
       AND h.source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
       AND h.record_source = 't24__t24_customer'
 ),
--- SAT: sat_customer_other — bản mới nhất &lt;= :DATADT, mỗi customer_hashkey
 cust_other AS (
     SELECT
         customer_hashkey,
@@ -481,7 +428,6 @@
     WHERE source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
     GROUP BY customer_hashkey
 ),
--- LINK: COMPANY_BOOK — link_customer_branch (con trỏ mới nhất &lt;= :DATADT) → hub_branch.business_key
 cust_branch_cur AS (
     SELECT
         customer_hashkey,
@@ -498,7 +444,6 @@
     JOIN IDENTIFIER(:cleaned || '.raw_vault.hub_branch') hb
         ON l.branch_hashkey = hb.branch_hashkey
 ),
--- LINK: ACCOUNT_OFFICER — link_customer_dept_acct_officer_nvql (con trỏ mới nhất &lt;= :DATADT) → hub_acct_officer.business_key
 cust_officer_cur AS (
     SELECT
         customer_hashkey,
@@ -519,7 +464,6 @@
     hub.customer_hashkey                                           AS IP_ID,
     hub.business_key                                               AS ID,
     DATE_FORMAT(pit.snapshot_date, 'yyyyMMdd')                     AS DATA_DATE,
-    -- sat_customer_information
     si.short_name                                                  AS T_SHORT_NAME,
     si.language                                                    AS T_LANGUAGE,
     TO_CHAR(TO_DATE(si.create_date, 'yyyyMMdd'), 'yyyyMMdd')::VARCHAR(8)      AS T_CREATE_DATE,
@@ -532,7 +476,6 @@
     TO_CHAR(TO_DATE(si.birth_incorp_date, 'yyyyMMdd'), 'yyyyMMdd')::VARCHAR(8) AS T_BIRTH_INCORP_DATE,
     si.residence                                                   AS T_RESIDENCE,
     si.nationality                                                 AS T_NATIONALITY,
-    -- sat_customer_contact
     sc.address                                                     AS T_ADDRESS,
     sc.town_country                                                AS T_TOWN_COUNTRY,
     sc.province_1                                                  AS T_PROVINCE_1,
@@ -545,26 +488,20 @@
     sc.sms_2                                                       AS T_SMS_2,
     sc.phone_2                                                     AS T_PHONE_2,
     sc.off_phone_2                                                 AS T_OFF_PHONE_2,
-    -- sat_customer_classification
     scl.sector                                                     AS T_SECTOR,
     scl.industry                                                   AS T_INDUSTRY,
     scl.cust_group                                                 AS T_CUST_GROUP,
-    -- sat_customer_kyc
     sk.tax_id                                                      AS T_TAX_ID,
     sk.legal_id                                                    AS T_LEGAL_ID,
     sk.legal_doc_name                                              AS T_LEGAL_DOC_NAME,
-    -- sat_customer_other
     TO_CHAR(TO_DATE(so.contact_date, 'yyyyMMdd'), 'yyyyMMdd')::VARCHAR(8)      AS T_CONTACT_DATE,
     so.province                                                    AS T_PROVINCE,
     so.fax_1                                                       AS T_FAX_1,
     so.email_2                                                     AS T_EMAIL_2,
-    -- sat_customer_financial_statement
     sf.net_monthly_in                                              AS T_NET_MONTHLY_IN,
     sf.total_property                                              AS T_TOTAL_PROPERTY,
     sf.total_income                                                AS T_TOTAL_INCOME,
-    -- link_customer_branch → hub_branch.business_key
     cb.company_book                                                AS T_COMPANY_BOOK,
-    -- link_customer_dept_acct_officer_nvql → hub_acct_officer.business_key
     ao.account_officer                                             AS T_ACCOUNT_OFFICER
 FROM IDENTIFIER(:cleaned || '.business_vault.pit_customer') pit
 LEFT JOIN cust_active hub
@@ -589,54 +526,22 @@
 LEFT JOIN cust_branch cb
     ON cb.customer_hashkey = hub.customer_hashkey
 LEFT JOIN cust_officer ao
-    ON ao.customer_hashkey = hub.customer_hashkey;
-</t>
+    ON ao.customer_hashkey = hub.customer_hashkey;</t>
   </si>
   <si>
     <t xml:space="preserve">USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tckh;
-CREATE TABLE IF NOT EXISTS T24_CRB (
-    MONTH_DAY       DECIMAL(4, 0),
-    DATA_DATE       DECIMAL(8, 0),
-    NGAY            STRING,
-    CHINHANH        STRING,
-    NGOAITE         STRING,
-    GL              STRING,
-    TIEUKHOAN       STRING,
-    TEN             STRING,
-    NGOAITE1        DECIMAL(20, 4),
-    NOITE           DECIMAL(20, 4),
-    SOTKCU          STRING,
-    LAISUAT         STRING,
-    KYHAN           STRING,
-    STARTDATE       STRING,
-    ENDDATE         STRING,
-    MASP            STRING,
-    LAIDATRA        STRING,
-    LOANCLASS       STRING,
-    CIF             DECIMAL(18, 0),
-    CATEGORY        DECIMAL(6, 0)
-)
-USING DELTA;
--- -------------------------------------------------------
--- STEP 1: Xóa dữ liệu cũ theo ngày
--- -------------------------------------------------------
 DELETE FROM T24_CRB
-WHERE DATA_DATE = CAST(:DATADT AS DECIMAL(8, 0));
--- -------------------------------------------------------
--- STEP 2: Nạp dữ liệu mới từ Raw Vault
--- -------------------------------------------------------
+WHERE DATA_DATE = CAST(:target_date AS DECIMAL(8, 0));
 INSERT INTO T24_CRB
 WITH
--- STS HUB: chỉ giữ key có trạng thái MỚI NHẤT (&lt;= :DATADT) = 'D'
 crb_sts_del AS (
     SELECT crb_hashkey
     FROM IDENTIFIER(:cleaned || '.raw_vault.sts_hub_crb')
-    WHERE source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
+    WHERE source_event_date &lt;= TO_DATE(:target_date, 'yyyyMMdd')
     GROUP BY crb_hashkey
     HAVING max_by(cdc_status, source_event_date) = 'D'
 ),
--- HUB active: hub CRB đã LOẠI key bị xóa (anti-join crb_sts_del)
 crb_active AS (
     SELECT
         h.crb_hashkey,
@@ -649,7 +554,6 @@
       AND d.crb_hashkey IS NULL
       AND h.tieukhoan != 'TOTAL'
 ),
--- MUL SAT: thông tin CRB — bản hiệu lực mới nhất &lt;= :DATADT, mỗi (crb_hashkey, ma_key)
 crb_info AS (
     SELECT
         crb_hashkey,
@@ -664,10 +568,9 @@
         max_by(loanclass, source_event_date) AS loanclass,
         max_by(ten,       source_event_date) AS ten
     FROM IDENTIFIER(:cleaned || '.raw_vault.sat_crb_information')
-    WHERE source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
+    WHERE source_event_date = TO_DATE(:target_date, 'yyyyMMdd')
     GROUP BY crb_hashkey, ma_key
 ),
--- MUL SAT: số dư CRB — bản hiệu lực mới nhất &lt;= :DATADT, mỗi (crb_hashkey, ma_key)
 crb_balance AS (
     SELECT
         crb_hashkey,
@@ -677,10 +580,9 @@
         max_by(noite,    source_event_date) AS noite,
         max_by(category, source_event_date) AS category
     FROM IDENTIFIER(:cleaned || '.raw_vault.sat_crb_balance')
-    WHERE source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
+    WHERE source_event_date = TO_DATE(:target_date, 'yyyyMMdd')
     GROUP BY crb_hashkey, ma_key
 ),
--- LINK: CHINHANH — link_crb_branch (con trỏ mới nhất &lt;= :DATADT) → hub_branch.business_key
 crb_branch_cur AS (
     SELECT
         crb_hashkey,
@@ -697,13 +599,12 @@
     JOIN IDENTIFIER(:cleaned || '.raw_vault.hub_branch') hb
         ON l.branch_hashkey = hb.branch_hashkey
 ),
--- LINK: CIF — link_crb_customer (con trỏ mới nhất &lt;= :DATADT) → hub_customer.business_key
 crb_customer_cur AS (
     SELECT
         crb_hashkey,
         max_by(customer_hashkey, source_event_date) AS customer_hashkey
     FROM IDENTIFIER(:cleaned || '.raw_vault.link_crb_customer')
-    WHERE source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
+    WHERE source_event_date &lt;= TO_DATE(:target_date, 'yyyyMMdd')
     GROUP BY crb_hashkey
 ),
 crb_customer AS (
@@ -715,45 +616,25 @@
         ON l.customer_hashkey = hc.customer_hashkey
 )
 SELECT
-    -- STT 1 | MONTH_DAY | DECIMAL(4,0) | transform: Right(DATADT, 4) → lấy MMDD
-    CAST(RIGHT(:DATADT, 4) AS DECIMAL(4, 0))                       AS MONTH_DAY,
-    -- STT 2 | DATA_DATE | DECIMAL(8,0) | transform: DATADT dạng yyyyMMdd
-    CAST(:DATADT AS DECIMAL(8, 0))                                 AS DATA_DATE,
-    -- STT 3 | NGAY | STRING | transform: = DATADT (yyyyMMdd)
-    :DATADT                                                        AS NGAY,
-    -- STT 4 | CHINHANH | link_crb_branch → hub_branch.business_key + bỏ newline
+    CAST(RIGHT(:target_date, 4) AS DECIMAL(4, 0))                       AS MONTH_DAY,
+    CAST(:target_date AS DECIMAL(8, 0))                                 AS DATA_DATE,
+    :target_date                                                        AS NGAY,
     REGEXP_REPLACE(cb.chinhanh, '[\r\n]', '')                      AS CHINHANH,
-    -- STT 5 | NGOAITE | sat_crb_balance
     sb.ngoaite                                                     AS NGOAITE,
-    -- STT 6 | GL | hub_crb.gl
     hub.gl                                                         AS GL,
-    -- STT 7 | TIEUKHOAN | hub_crb.tieukhoan
     hub.tieukhoan                                                  AS TIEUKHOAN,
-    -- STT 8 | TEN | sat_crb_information
     si.ten                                                         AS TEN,
-    -- STT 9 | NGOAITE1 | sat_crb_balance
     sb.ngoaite1                                                    AS NGOAITE1,
-    -- STT 10 | NOITE | sat_crb_balance
     sb.noite                                                       AS NOITE,
-    -- STT 11 | SOTKCU | sat_crb_information
     si.sotkcu                                                      AS SOTKCU,
-    -- STT 12 | LAISUAT | sat_crb_information
     si.laisuat                                                     AS LAISUAT,
-    -- STT 13 | KYHAN | sat_crb_information
     si.kyhan                                                       AS KYHAN,
-    -- STT 14 | STARTDATE | sat_crb_information
     si.startdate                                                   AS STARTDATE,
-    -- STT 15 | ENDDATE | transform: IF ENDDATE = 0 THEN NULL
     NULLIF(si.enddate, 0)                                          AS ENDDATE,
-    -- STT 16 | MASP | sat_crb_information
     si.masp                                                        AS MASP,
-    -- STT 17 | LAIDATRA | sat_crb_information
     si.laidatra                                                    AS LAIDATRA,
-    -- STT 18 | LOANCLASS | sat_crb_information
     si.loanclass                                                   AS LOANCLASS,
-    -- STT 19 | CIF | link_crb_customer → hub_customer.business_key
     cc.cif                                                         AS CIF,
-    -- STT 20 | CATEGORY | sat_crb_balance
     sb.category                                                    AS CATEGORY
 FROM crb_active hub
 LEFT JOIN crb_info si
@@ -770,20 +651,25 @@
   <si>
     <t>USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tckh;
-CREATE OR REPLACE VIEW branch_list AS
+CREATE OR REPLACE VIEW BRANCH_LIST AS
 SELECT
-    dim.OU_ID       AS OU_ID,
-    dim.OU_CODE     AS BRANCH_CODE,
-    dim.OU_NM       AS BRANCH_NAME,
-    dim.PRN_OU_CODE AS PRN_BRANCH_CODE,
-    dim.PRN_OU_NM   AS PRN_BRANCH_NAME
+      dim.OU_ID           AS OU_ID
+    , dim.OU_CODE         AS BRANCH_CODE
+    , dim.OU_NM           AS BRANCH_NAME
+    , nvl(dim.PRN_OU_CODE, dim.OU_CODE)     AS PRN_BRANCH_CODE
+    , nvl(dim.PRN_OU_NM, dim.OU_NM)       AS PRN_BRANCH_NAME
 FROM CB_OU_DIM dim
-WHERE dim.EFF_TO_DT IS NULL;</t>
-  </si>
-  <si>
-    <t>USE CATALOG IDENTIFIER(:curated);
+WHERE dim.EFF_TO_DT IS NULL   -- SCD2: chỉ lấy bản ghi còn hiệu lực (NULL = chưa đóng)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tckh;
-CREATE OR REPLACE TABLE holiday AS
+INSERT OVERWRITE holiday (
+    DATA_DATE_DT,
+    HOLIDAY_DATE_DT,
+    DATA_DT,
+    HOLIDAY_DT
+)
 SELECT
     TO_DATE(CAST(MAX(W.msr_prd_id) AS STRING), 'yyyyMMdd')   AS DATA_DATE_DT,
     TO_DATE(CAST(D.msr_prd_id AS STRING), 'yyyyMMdd')        AS HOLIDAY_DATE_DT,
@@ -794,12 +680,21 @@
     ON  D.msr_prd_id &gt; W.msr_prd_id
     AND W.bsn_day_f = 1
 WHERE D.bsn_day_f = 0
-GROUP BY D.msr_prd_id;</t>
+GROUP BY D.msr_prd_id;
+</t>
   </si>
   <si>
     <t xml:space="preserve">USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tckh;
-CREATE OR REPLACE TABLE working_day AS
+INSERT OVERWRITE working_day (
+    DATA_DT,
+    FROM_DATE_DT,
+    FROM_DT,
+    END_DT,
+    END_DATE_DT,
+    BEGIN_OF_MONTH,
+    BEGIN_OF_MONTH_DATE
+)
 WITH
 v_from_dt AS (
     SELECT
@@ -871,7 +766,6 @@
 USE SCHEMA tckh;
 CREATE OR REPLACE VIEW v_t24_crb_fulllist AS
 WITH
--- STS HUB: chỉ giữ key SECURITY có trạng thái MỚI NHẤT (&lt;= :DATADT) = 'D'
 security_sts_del AS (
     SELECT security_hashkey
     FROM IDENTIFIER(:cleaned || '.raw_vault.sts_hub_security')
@@ -879,7 +773,6 @@
     GROUP BY security_hashkey
     HAVING max_by(cdc_status, source_event_date) = 'D'
 ),
--- HUB active: hub SECURITY đã LOẠI key bị xóa (anti-join security_sts_del)
 security_active AS (
     SELECT
         h.security_hashkey,
@@ -891,7 +784,6 @@
       AND h.source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
       AND h.record_source = 't24__t24_security_master'
 ),
--- SAT: thông tin cơ bản (COMPANY_NAME) — bản hiệu lực mới nhất &lt;= :DATADT
 security_info AS (
     SELECT
         security_hashkey,
@@ -957,29 +849,9 @@
   <si>
     <t>USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tckh;
-CREATE TABLE IF NOT EXISTS CB_OU_DIM (
-    OU_DIM_ID       BIGINT,     -- MAX(OU_DIM_ID) + ROW_NUMBER()
-    OU_ID           STRING,     -- branch_hashkey (SHA256)
-    OU_NM           STRING,
-    OU_CODE         STRING,
-    PRN_OU_ID       STRING,
-    PRN_OU_NM       STRING,
-    PRN_OU_CODE     STRING,
-    CB_AREA_ID      INTEGER,
-    CB_AREA_NM      STRING,
-    CRT_TM          TIMESTAMP,
-    EFF_FM_DT       DATE,
-    EFF_TO_DT       DATE,
-    START_WK_DT     DATE,
-    OU_ADR          STRING,
-    OU_PH           STRING,
-    CDC_FLAG        STRING
-)
-USING DELTA;
 MERGE INTO CB_OU_DIM tgt
 USING (
     WITH
-    -- STS Hub: khóa có trạng thái mới nhất = 'D' (đã xóa) đến :etl_date
     sts_deleted AS (
         SELECT branch_hashkey
         FROM IDENTIFIER(:cleaned || '.raw_vault.sts_hub_branch')
@@ -987,15 +859,12 @@
         GROUP BY branch_hashkey
         HAVING MAX_BY(cdc_status, source_event_date) = 'D'
     ),
-    -- Hub đang có hiệu lực = Hub LEFT JOIN loại các khóa deleted
     hub_active AS (
         SELECT h.branch_hashkey, h.business_key, h.source_event_date
         FROM IDENTIFIER(:cleaned || '.raw_vault.hub_branch') h
-        LEFT JOIN sts_deleted d
-            ON h.branch_hashkey = d.branch_hashkey
+        LEFT JOIN sts_deleted d ON h.branch_hashkey = d.branch_hashkey
         WHERE d.branch_hashkey IS NULL
     ),
-    -- Satellite (single-active): làm giàu thuộc tính, bản mới nhất đến :etl_date
     sat_latest AS (
         SELECT
             branch_hashkey,
@@ -1004,7 +873,6 @@
         WHERE source_event_date &lt;= TO_DATE(:etl_date, 'yyyyMMdd')
         GROUP BY branch_hashkey
     ),
-    -- Satellite branch_mapping (single-active)
     bm_latest AS (
         SELECT
             branch_hashkey,
@@ -1015,18 +883,23 @@
         WHERE source_event_date &lt;= TO_DATE(:etl_date, 'yyyyMMdd')
         GROUP BY branch_hashkey
     ),
+    area_map AS (
+        SELECT OU_ID, CB_AREA_ID, CB_AREA_NM
+        FROM ou_area_mapping
+        WHERE CB_AREA_ID IS NOT NULL
+    ),
     source_data AS (
         SELECT
-            h.branch_hashkey                                    AS OU_ID,
-            h.business_key                                      AS OU_CODE,
-            SUBSTRING_INDEX(si.t_company_name, '::', 1)         AS OU_NM,
-            prn_hub.branch_hashkey                              AS PRN_OU_ID,
-            SUBSTRING_INDEX(prn_si.t_company_name, '::', 1)     AS PRN_OU_NM,
-            bm.parent_branch_code                               AS PRN_OU_CODE,
+            h.branch_hashkey                                AS OU_ID,
+            h.business_key                                  AS OU_CODE,
+            SUBSTRING_INDEX(si.t_company_name, '::', 1)     AS OU_NM,
+            prn_hub.branch_hashkey                          AS PRN_OU_ID,
+            SUBSTRING_INDEX(prn_si.t_company_name, '::', 1) AS PRN_OU_NM,
+            bm.parent_branch_code                           AS PRN_OU_CODE,
             am.CB_AREA_ID,
             am.CB_AREA_NM,
-            bm.address                                          AS OU_ADR,
-            bm.phone_number                                     AS OU_PH,
+            bm.address                                      AS OU_ADR,
+            bm.phone_number                                 AS OU_PH,
             h.source_event_date
         FROM hub_active h
         LEFT JOIN sat_latest si
@@ -1037,15 +910,10 @@
             ON prn_hub.business_key = bm.parent_branch_code
         LEFT JOIN sat_latest prn_si
             ON prn_hub.branch_hashkey = prn_si.branch_hashkey
-        LEFT JOIN ou_area_mapping am
+        LEFT JOIN area_map am
             ON am.OU_ID = h.business_key
         WHERE UPPER(COALESCE(si.t_company_name, '')) &lt;&gt; 'NOT USED'
           AND h.business_key &lt;&gt; 'VN0010001'
-    ),
-    -- Max OU_DIM_ID hiện tại
-    max_id AS (
-        SELECT COALESCE(MAX(OU_DIM_ID), 0) AS max_val
-        FROM CB_OU_DIM
     ),
     changed AS (
         SELECT src.OU_ID
@@ -1063,6 +931,7 @@
     new_records AS (
         SELECT
             'NEW'                                               AS rec_type,
+            CASE WHEN tgt_chk.OU_ID IS NULL THEN 'I' ELSE 'U' END AS CDC_FLAG,
             src.OU_ID,
             src.OU_NM,
             src.OU_CODE,
@@ -1074,10 +943,8 @@
             src.source_event_date,
             src.OU_ADR,
             src.OU_PH,
-            CASE WHEN tgt_chk.OU_ID IS NULL THEN 'I' ELSE 'U' END AS CDC_FLAG,
-            m.max_val + ROW_NUMBER() OVER (ORDER BY src.OU_ID)  AS NEW_OU_DIM_ID
+            uuid()                                              AS NEW_OU_DIM_ID
         FROM source_data src
-        CROSS JOIN max_id m
         LEFT JOIN CB_OU_DIM tgt_chk
             ON  src.OU_ID        = tgt_chk.OU_ID
             AND tgt_chk.EFF_TO_DT IS NULL
@@ -1086,7 +953,8 @@
     ),
     close_records AS (
         SELECT
-            'CLOSE'                                             AS rec_type,
+            'CLOSE'                AS rec_type,
+            'D'                    AS CDC_FLAG,
             tgt.OU_ID,
             tgt.OU_NM,
             tgt.OU_CODE,
@@ -1095,11 +963,10 @@
             tgt.PRN_OU_CODE,
             tgt.CB_AREA_ID,
             tgt.CB_AREA_NM,
-            tgt.START_WK_DT                                     AS source_event_date,
+            tgt.START_WK_DT        AS source_event_date,
             tgt.OU_ADR,
             tgt.OU_PH,
-            'D'                                                 AS CDC_FLAG,
-            tgt.OU_DIM_ID                                       AS NEW_OU_DIM_ID
+            tgt.OU_DIM_ID          AS NEW_OU_DIM_ID 
         FROM CB_OU_DIM tgt
         LEFT JOIN source_data src ON src.OU_ID = tgt.OU_ID
         WHERE tgt.EFF_TO_DT IS NULL
@@ -1108,9 +975,25 @@
                 OR src.OU_ID IS NULL
               )
     )
-    SELECT * FROM new_records
+    SELECT
+        rec_type, CDC_FLAG,
+        OU_ID, OU_NM, OU_CODE,
+        PRN_OU_ID, PRN_OU_NM, PRN_OU_CODE,
+        CB_AREA_ID, CB_AREA_NM,
+        source_event_date,
+        OU_ADR, OU_PH,
+        NEW_OU_DIM_ID
+    FROM new_records
     UNION ALL
-    SELECT * FROM close_records
+    SELECT
+        rec_type, CDC_FLAG,
+        OU_ID, OU_NM, OU_CODE,
+        PRN_OU_ID, PRN_OU_NM, PRN_OU_CODE,
+        CB_AREA_ID, CB_AREA_NM,
+        source_event_date,
+        OU_ADR, OU_PH,
+        NEW_OU_DIM_ID
+    FROM close_records
 ) src
 ON  tgt.OU_ID     = src.OU_ID
 AND tgt.EFF_TO_DT IS NULL
@@ -1122,7 +1005,7 @@
         PRN_OU_ID, PRN_OU_NM, PRN_OU_CODE,
         CB_AREA_ID, CB_AREA_NM,
         CRT_TM, EFF_FM_DT, EFF_TO_DT, START_WK_DT,
-        OU_ADR, OU_PH, CDC_FLAG
+        OU_ADR, OU_PH
     )
     VALUES (
         src.NEW_OU_DIM_ID,
@@ -1139,121 +1022,37 @@
         NULL,
         src.source_event_date,
         src.OU_ADR,
-        src.OU_PH,
-        src.CDC_FLAG
+        src.OU_PH
     )
 WHEN MATCHED AND src.rec_type = 'CLOSE' THEN
     UPDATE SET
         tgt.EFF_TO_DT = DATE_SUB(TO_DATE(:etl_date, 'yyyyMMdd'), 1),
-        tgt.CDC_FLAG  = 'D',
-        tgt.CRT_TM    = CURRENT_TIMESTAMP()
-;</t>
-  </si>
-  <si>
-    <t>HOLIDAY — VIEW
-JOIN SCHEMA — HOLIDAY</t>
-  </si>
-  <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>Table / View</t>
-  </si>
-  <si>
-    <t>Alias</t>
-  </si>
-  <si>
-    <t>JOIN Type</t>
-  </si>
-  <si>
-    <t>ON Condition / Ghi chú</t>
-  </si>
-  <si>
-    <t>calendar</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>BASE</t>
-  </si>
-  <si>
-    <t>FROM ocb_datavault_pilotcloud_cleaned.business_vault.calendar D
-WHERE D.bsn_day_f = 0    -- D là ngày nghỉ
-GROUP BY D.msr_prd_id
-ORDER BY D.msr_prd_id;</t>
-  </si>
-  <si>
-    <t>W</t>
-  </si>
-  <si>
-    <t>LEFT JOIN</t>
-  </si>
-  <si>
-    <t>LEFT JOIN ocb_datavault_pilotcloud_cleaned.business_vault.calendar W
-    ON D.msr_prd_id &gt; W.msr_prd_id
-    AND W.bsn_day_f = 1   -- W là ngày làm việc</t>
-  </si>
-  <si>
-    <t>Cơ chế: lấy dữ liệu ngày mới (TRUNCATE THEN INSERT)</t>
-  </si>
-  <si>
-    <t>FIELD MAPPING — HOLIDAY</t>
-  </si>
-  <si>
-    <t>Field (Output Col)</t>
-  </si>
-  <si>
-    <t>DataType</t>
-  </si>
-  <si>
-    <t>TransformType</t>
-  </si>
-  <si>
-    <t>Transform Logic</t>
-  </si>
-  <si>
-    <t>DATA_DATE_DT</t>
-  </si>
-  <si>
-    <t>timestamp</t>
-  </si>
-  <si>
-    <t>TRANSFORM</t>
-  </si>
-  <si>
-    <t>TO_DATE(CAST(MAX(W.MSR_PRD_ID) AS STRING), 'yyyyMMdd')</t>
-  </si>
-  <si>
-    <t>HOLIDAY_DATE_DT</t>
-  </si>
-  <si>
-    <t>TO_DATE(CAST(D.MSR_PRD_ID AS STRING), 'yyyyMMdd')</t>
-  </si>
-  <si>
-    <t>DATA_DT</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>MAX(W.MSR_PRD_ID)</t>
-  </si>
-  <si>
-    <t>HOLIDAY_DT</t>
-  </si>
-  <si>
-    <t>1:1</t>
-  </si>
-  <si>
-    <t>D.MSR_PRD_ID</t>
+        tgt.CRT_TM    = CURRENT_TIMESTAMP()</t>
   </si>
   <si>
     <t>V_T24_CRB_FULLLIST
 JOIN SCHEMA — V_T24_CRB_FULLLIST</t>
   </si>
   <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Table / View</t>
+  </si>
+  <si>
+    <t>Alias</t>
+  </si>
+  <si>
+    <t>JOIN Type</t>
+  </si>
+  <si>
+    <t>ON Condition / Ghi chú</t>
+  </si>
+  <si>
     <t>A</t>
+  </si>
+  <si>
+    <t>BASE</t>
   </si>
   <si>
     <t>FROM T24_CRB A WITH (NOLOCK)
@@ -1320,6 +1119,9 @@
     <t>B</t>
   </si>
   <si>
+    <t>LEFT JOIN</t>
+  </si>
+  <si>
     <t xml:space="preserve">ON A.DATA_DATE = B.DATA_DATE 
 AND SUBSTRING(A.TIEUKHOAN,12,99) = B.ID) 
 </t>
@@ -1328,6 +1130,9 @@
     <t>t_cust as (
 select DATA_DATE, ID, T_SHORT_NAME from T24_CUSTOMER with (nolock) where DATA_DATE &gt;= 20240601
 )</t>
+  </si>
+  <si>
+    <t>D</t>
   </si>
   <si>
     <t xml:space="preserve"> ON A.DATA_DATE = D.DATA_DATE 
@@ -1343,6 +1148,9 @@
 )</t>
   </si>
   <si>
+    <t>W</t>
+  </si>
+  <si>
     <t xml:space="preserve">ON A.DATA_DATE = W.DATA_DT
 </t>
   </si>
@@ -1357,12 +1165,18 @@
     <t>Transform Type</t>
   </si>
   <si>
+    <t>Transform Logic</t>
+  </si>
+  <si>
     <t>SOURCE</t>
   </si>
   <si>
     <t>CDR_DT_ID</t>
   </si>
   <si>
+    <t>1:1</t>
+  </si>
+  <si>
     <t>A.DATA_DATE</t>
   </si>
   <si>
@@ -1475,354 +1289,6 @@
   </si>
   <si>
     <t>A.MASP</t>
-  </si>
-  <si>
-    <t>working_day — VIEW
-JOIN SCHEMA — WORKING_DAY</t>
-  </si>
-  <si>
-    <t>v_from_dt AS (
-    SELECT 
-        D.msr_prd_id                                                          AS DATA_DT,
-        DATE_FORMAT(
-            MAX(TO_DATE(CAST(B.msr_prd_id AS STRING), 'yyyyMMdd')) + INTERVAL 1 DAY,
-            'yyyyMMdd'
-        )                                                                     AS FROM_DT,
-        MAX(TO_DATE(CAST(B.msr_prd_id AS STRING), 'yyyyMMdd')) + INTERVAL 1 DAY AS FROM_DATE_DT
-    FROM ocb_datavault_pilotcloud_cleaned.business_vault.calendar D
-    LEFT JOIN ocb_datavault_pilotcloud_cleaned.business_vault.calendar B
-        ON D.msr_prd_id &gt; B.msr_prd_id
-        AND B.bsn_day_f = 1   -- B là ngày làm việc trước D
-    WHERE D.bsn_day_f = 1     -- D là ngày làm việc
-    GROUP BY D.msr_prd_id
-)</t>
-  </si>
-  <si>
-    <t>v_end_dt AS (
-    SELECT 
-        D.msr_prd_id                                                          AS DATA_DT,
-        DATE_FORMAT(
-            MIN(TO_DATE(CAST(E.msr_prd_id AS STRING), 'yyyyMMdd')) - INTERVAL 1 DAY,
-            'yyyyMMdd'
-        )                                                                     AS END_DT,
-        MIN(TO_DATE(CAST(E.msr_prd_id AS STRING), 'yyyyMMdd')) - INTERVAL 1 DAY AS END_DATE_DT
-    FROM ocb_datavault_pilotcloud_cleaned.business_vault.calendar D
-    LEFT JOIN ocb_datavault_pilotcloud_cleaned.business_vault.calendar E
-        ON D.msr_prd_id &lt; E.msr_prd_id
-        AND E.bsn_day_f = 1 
-    WHERE D.bsn_day_f = 1    
-    GROUP BY D.msr_prd_id
-)</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>JOIN</t>
-  </si>
-  <si>
-    <t>ON B.DATA_DT = E.DATA_DT</t>
-  </si>
-  <si>
-    <t>Cơ chế: lấy dữ liệu ngày mới (TRUNCATE xpng INSERT)</t>
-  </si>
-  <si>
-    <t>FIELD MAPPING — WORKING_DAY</t>
-  </si>
-  <si>
-    <t>working_day</t>
-  </si>
-  <si>
-    <t>E.DATA_DT</t>
-  </si>
-  <si>
-    <t>FROM_DATE_DT</t>
-  </si>
-  <si>
-    <t>date</t>
-  </si>
-  <si>
-    <t>TO_DATE( CASE WHEN SUBSTR(B.FROM_DT,1,6) &lt; SUBSTR(CAST(B.DATA_DT AS STRING),1,6) OR SUBSTR(B.FROM_DT,7,2) = '01'
-            THEN CONCAT(SUBSTR(CAST(B.DATA_DT AS STRING),1,6),'01')
-            ELSE CAST(B.DATA_DT AS STRING)
-        END, 'yyyyMMdd') AS FROM_DATE_DT</t>
-  </si>
-  <si>
-    <t>FROM_DT</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>CONCAT(SUBSTR(CAST(B.DATA_DT AS STRING),1,6),'01')</t>
-  </si>
-  <si>
-    <t>END_DT</t>
-  </si>
-  <si>
-    <t>CAST(B.DATA_DT AS STRING)</t>
-  </si>
-  <si>
-    <t>END_DATE_DT</t>
-  </si>
-  <si>
-    <t>END, 'yyyyMMdd') AS FROM_DATE_DT</t>
-  </si>
-  <si>
-    <t>BEGIN_OF_MONTH</t>
-  </si>
-  <si>
-    <t>CASE WHEN SUBSTR(B.FROM_DT,1,6) &lt; SUBSTR(CAST(B.DATA_DT AS STRING),1,6) OR SUBSTR(B.FROM_DT,7,2) = '01'</t>
-  </si>
-  <si>
-    <t>BEGIN_OF_MONTH_DATE</t>
-  </si>
-  <si>
-    <t>THEN CONCAT(SUBSTR(CAST(B.DATA_DT AS STRING),1,6),'01')</t>
-  </si>
-  <si>
-    <t>LV2 — View/Table được JOIN trực tiếp trong LV1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JOIN SCHEMA </t>
-  </si>
-  <si>
-    <t>WHERE dim.EFF_TO_DT IS NULL</t>
-  </si>
-  <si>
-    <t>FIELD MAPPING — LV2</t>
-  </si>
-  <si>
-    <t>Field</t>
-  </si>
-  <si>
-    <t>PRN_BRANCH_NAME</t>
-  </si>
-  <si>
-    <t>PRN_OU_NM</t>
-  </si>
-  <si>
-    <t>PRN_OU_CODE</t>
-  </si>
-  <si>
-    <t>BRANCH_CODE</t>
-  </si>
-  <si>
-    <t>OU_NM</t>
-  </si>
-  <si>
-    <t>PRN_BRANCH_CODE</t>
-  </si>
-  <si>
-    <t>OU_CODE</t>
-  </si>
-  <si>
-    <t>OU_ID</t>
-  </si>
-  <si>
-    <t>JOIN SCHEMA</t>
-  </si>
-  <si>
-    <t>hub_active AS (
-    SELECT
-        h.branch_hashkey,
-        h.business_key,
-        h.source_event_date
-    FROM ocb_datavault_dev_cleaned.raw_vault.hub_branch h
-    LEFT JOIN (
-        SELECT branch_hashkey, cdc_status
-        FROM (
-            SELECT
-                branch_hashkey,
-                cdc_status,
-                ROW_NUMBER() OVER (PARTITION BY branch_hashkey ORDER BY source_event_date DESC) AS rn
-            FROM ocb_datavault_dev_cleaned.raw_vault.sts_hub_branch
-        ) t
-        WHERE rn = 1
-    ) sts ON h.branch_hashkey = sts.branch_hashkey
-    WHERE COALESCE(sts.cdc_status, 'I') &lt;&gt; 'D'
-)</t>
-  </si>
-  <si>
-    <t>hub</t>
-  </si>
-  <si>
-    <t>FROM hub_active hub
-WHERE UPPER(COALESCE(si.t_company_name, '')) &lt;&gt; 'NOT USED'
-  AND hub.business_key &lt;&gt; 'VN0010001'</t>
-  </si>
-  <si>
-    <t>sat_info AS (
-    SELECT branch_hashkey, t_mnemonic, t_company_name
-    FROM (
-        SELECT
-            branch_hashkey,
-            t_mnemonic,
-            t_company_name,
-            ROW_NUMBER() OVER (PARTITION BY branch_hashkey ORDER BY source_event_date DESC) AS rn
-        FROM ocb_datavault_dev_cleaned.raw_vault.sat_branch_information
-    ) t
-    WHERE rn = 1
-)</t>
-  </si>
-  <si>
-    <t>si</t>
-  </si>
-  <si>
-    <t>ON hub.branch_hashkey = si.branch_hashkey</t>
-  </si>
-  <si>
-    <t>branch_mapping</t>
-  </si>
-  <si>
-    <t>bm</t>
-  </si>
-  <si>
-    <t>ON bm.BRANCH_CODE = hub.business_key</t>
-  </si>
-  <si>
-    <t>hub_active (self)</t>
-  </si>
-  <si>
-    <t>prn_hub</t>
-  </si>
-  <si>
-    <t>ON prn_hub.business_key = bm.PARENT_BRANCH_CODE</t>
-  </si>
-  <si>
-    <t>sat_info (join lần 2)</t>
-  </si>
-  <si>
-    <t>prn_si</t>
-  </si>
-  <si>
-    <t>ON prn_hub.branch_hashkey = prn_si.branch_hashkey</t>
-  </si>
-  <si>
-    <t>ou_area_mapping</t>
-  </si>
-  <si>
-    <t>am</t>
-  </si>
-  <si>
-    <t>ON CAST(am.OU_DW_ID AS STRING) = CAST(hub.branch_hashkey AS STRING)</t>
-  </si>
-  <si>
-    <t>max_id AS (
-    SELECT NVL(MAX(OU_DIM_ID), 0) AS MAX_OU_DIM_ID
-    FROM ocb_datavault_dev_curated.tckh.CB_OU_DIM
-)</t>
-  </si>
-  <si>
-    <t>CROSS JOIN</t>
-  </si>
-  <si>
-    <t>Note: đây là bảng SCD TYPE 2</t>
-  </si>
-  <si>
-    <t>Target Table</t>
-  </si>
-  <si>
-    <t>Fields</t>
-  </si>
-  <si>
-    <t>Data Type</t>
-  </si>
-  <si>
-    <t>OU_DIM_ID</t>
-  </si>
-  <si>
-    <t>BIGINT</t>
-  </si>
-  <si>
-    <t>transform</t>
-  </si>
-  <si>
-    <t>NVL(MAX(OU_DIM_ID),0) + ROW_NUMBER() OVER (ORDER BY hub.branch_hashkey)</t>
-  </si>
-  <si>
-    <t>STRING</t>
-  </si>
-  <si>
-    <t>hub.branch_hashkey</t>
-  </si>
-  <si>
-    <t>hub_branch</t>
-  </si>
-  <si>
-    <t>SUBSTRING_INDEX(si.t_company_name, '::', 1)</t>
-  </si>
-  <si>
-    <t>sat_branch_information</t>
-  </si>
-  <si>
-    <t>hub.business_key</t>
-  </si>
-  <si>
-    <t>PRN_OU_ID</t>
-  </si>
-  <si>
-    <t>prn_hub.branch_hashkey</t>
-  </si>
-  <si>
-    <t>SUBSTRING_INDEX(prn_si.t_company_name, '::', 1)</t>
-  </si>
-  <si>
-    <t>CB_AREA_ID</t>
-  </si>
-  <si>
-    <t>am.CB_AREA_ID</t>
-  </si>
-  <si>
-    <t>CB_AREA_NM</t>
-  </si>
-  <si>
-    <t>am.CB_AREA_NM</t>
-  </si>
-  <si>
-    <t>CRT_TM</t>
-  </si>
-  <si>
-    <t>TIMESTAMP</t>
-  </si>
-  <si>
-    <t>CURRENT_TIMESTAMP()</t>
-  </si>
-  <si>
-    <t>EFF_FM_DT</t>
-  </si>
-  <si>
-    <t>DATE</t>
-  </si>
-  <si>
-    <t>constant</t>
-  </si>
-  <si>
-    <t>NULL</t>
-  </si>
-  <si>
-    <t>EFF_TO_DT</t>
-  </si>
-  <si>
-    <t>bm.PARENT_BRANCH_CODE</t>
-  </si>
-  <si>
-    <t>START_WK_DT</t>
-  </si>
-  <si>
-    <t>hub.source_event_date</t>
-  </si>
-  <si>
-    <t>OU_ADR</t>
-  </si>
-  <si>
-    <t>bm.ADDRESS</t>
-  </si>
-  <si>
-    <t>OU_PH</t>
-  </si>
-  <si>
-    <t>bm.PHONE_NUMBER</t>
   </si>
   <si>
     <t xml:space="preserve">T24_CRB
@@ -1853,6 +1319,9 @@
 )</t>
   </si>
   <si>
+    <t>hub</t>
+  </si>
+  <si>
     <t xml:space="preserve">FROM hub_active hub
 </t>
   </si>
@@ -1875,6 +1344,9 @@
     ),</t>
   </si>
   <si>
+    <t>si</t>
+  </si>
+  <si>
     <t xml:space="preserve">ON hub.crb_hashkey = si.crb_hashkey
 </t>
   </si>
@@ -1955,6 +1427,12 @@
     <t>FIELD MAPPING (T24_CRB)</t>
   </si>
   <si>
+    <t>Field</t>
+  </si>
+  <si>
+    <t>DataType</t>
+  </si>
+  <si>
     <t>Transform
 Type</t>
   </si>
@@ -1983,10 +1461,16 @@
     <t>NGAY</t>
   </si>
   <si>
+    <t>string</t>
+  </si>
+  <si>
     <t xml:space="preserve">TO_DATE(:p_data_date, 'yyyyMMdd') </t>
   </si>
   <si>
     <t>REGEXP_REPLACE(cb.chinhanh, '[\r\n]','')</t>
+  </si>
+  <si>
+    <t>hub_branch</t>
   </si>
   <si>
     <t>sb.ngoaite</t>
@@ -2166,6 +1650,9 @@
     <t>IP_ID</t>
   </si>
   <si>
+    <t>int</t>
+  </si>
+  <si>
     <t>hub.customer_hashkey</t>
   </si>
   <si>
@@ -2175,6 +1662,9 @@
     <t>decimal(10, 0)</t>
   </si>
   <si>
+    <t>hub.business_key</t>
+  </si>
+  <si>
     <t>pit.snapshot_date</t>
   </si>
   <si>
@@ -2443,6 +1933,396 @@
   </si>
   <si>
     <t>hub_acct_officer</t>
+  </si>
+  <si>
+    <t>LV2 — View/Table được JOIN trực tiếp trong LV1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOIN SCHEMA </t>
+  </si>
+  <si>
+    <t>WHERE dim.EFF_TO_DT IS NULL</t>
+  </si>
+  <si>
+    <t>FIELD MAPPING — LV2</t>
+  </si>
+  <si>
+    <t>PRN_BRANCH_NAME</t>
+  </si>
+  <si>
+    <t>PRN_OU_NM</t>
+  </si>
+  <si>
+    <t>PRN_OU_CODE</t>
+  </si>
+  <si>
+    <t>BRANCH_CODE</t>
+  </si>
+  <si>
+    <t>OU_NM</t>
+  </si>
+  <si>
+    <t>PRN_BRANCH_CODE</t>
+  </si>
+  <si>
+    <t>OU_CODE</t>
+  </si>
+  <si>
+    <t>OU_ID</t>
+  </si>
+  <si>
+    <t>JOIN SCHEMA</t>
+  </si>
+  <si>
+    <t>hub_active AS (
+    SELECT
+        h.branch_hashkey,
+        h.business_key,
+        h.source_event_date
+    FROM ocb_datavault_dev_cleaned.raw_vault.hub_branch h
+    LEFT JOIN (
+        SELECT branch_hashkey, cdc_status
+        FROM (
+            SELECT
+                branch_hashkey,
+                cdc_status,
+                ROW_NUMBER() OVER (PARTITION BY branch_hashkey ORDER BY source_event_date DESC) AS rn
+            FROM ocb_datavault_dev_cleaned.raw_vault.sts_hub_branch
+        ) t
+        WHERE rn = 1
+    ) sts ON h.branch_hashkey = sts.branch_hashkey
+    WHERE COALESCE(sts.cdc_status, 'I') &lt;&gt; 'D'
+)</t>
+  </si>
+  <si>
+    <t>FROM hub_active hub
+WHERE UPPER(COALESCE(si.t_company_name, '')) &lt;&gt; 'NOT USED'
+  AND hub.business_key &lt;&gt; 'VN0010001'</t>
+  </si>
+  <si>
+    <t>sat_info AS (
+    SELECT branch_hashkey, t_mnemonic, t_company_name
+    FROM (
+        SELECT
+            branch_hashkey,
+            t_mnemonic,
+            t_company_name,
+            ROW_NUMBER() OVER (PARTITION BY branch_hashkey ORDER BY source_event_date DESC) AS rn
+        FROM ocb_datavault_dev_cleaned.raw_vault.sat_branch_information
+    ) t
+    WHERE rn = 1
+)</t>
+  </si>
+  <si>
+    <t>ON hub.branch_hashkey = si.branch_hashkey</t>
+  </si>
+  <si>
+    <t>branch_mapping</t>
+  </si>
+  <si>
+    <t>bm</t>
+  </si>
+  <si>
+    <t>ON bm.BRANCH_CODE = hub.business_key</t>
+  </si>
+  <si>
+    <t>hub_active (self)</t>
+  </si>
+  <si>
+    <t>prn_hub</t>
+  </si>
+  <si>
+    <t>ON prn_hub.business_key = bm.PARENT_BRANCH_CODE</t>
+  </si>
+  <si>
+    <t>sat_info (join lần 2)</t>
+  </si>
+  <si>
+    <t>prn_si</t>
+  </si>
+  <si>
+    <t>ON prn_hub.branch_hashkey = prn_si.branch_hashkey</t>
+  </si>
+  <si>
+    <t>ou_area_mapping</t>
+  </si>
+  <si>
+    <t>am</t>
+  </si>
+  <si>
+    <t>ON CAST(am.OU_DW_ID AS STRING) = CAST(hub.branch_hashkey AS STRING)</t>
+  </si>
+  <si>
+    <t>max_id AS (
+    SELECT NVL(MAX(OU_DIM_ID), 0) AS MAX_OU_DIM_ID
+    FROM ocb_datavault_dev_curated.tckh.CB_OU_DIM
+)</t>
+  </si>
+  <si>
+    <t>CROSS JOIN</t>
+  </si>
+  <si>
+    <t>Note: đây là bảng SCD TYPE 2</t>
+  </si>
+  <si>
+    <t>Target Table</t>
+  </si>
+  <si>
+    <t>Fields</t>
+  </si>
+  <si>
+    <t>Data Type</t>
+  </si>
+  <si>
+    <t>OU_DIM_ID</t>
+  </si>
+  <si>
+    <t>BIGINT</t>
+  </si>
+  <si>
+    <t>transform</t>
+  </si>
+  <si>
+    <t>NVL(MAX(OU_DIM_ID),0) + ROW_NUMBER() OVER (ORDER BY hub.branch_hashkey)</t>
+  </si>
+  <si>
+    <t>STRING</t>
+  </si>
+  <si>
+    <t>hub.branch_hashkey</t>
+  </si>
+  <si>
+    <t>SUBSTRING_INDEX(si.t_company_name, '::', 1)</t>
+  </si>
+  <si>
+    <t>sat_branch_information</t>
+  </si>
+  <si>
+    <t>PRN_OU_ID</t>
+  </si>
+  <si>
+    <t>prn_hub.branch_hashkey</t>
+  </si>
+  <si>
+    <t>SUBSTRING_INDEX(prn_si.t_company_name, '::', 1)</t>
+  </si>
+  <si>
+    <t>CB_AREA_ID</t>
+  </si>
+  <si>
+    <t>am.CB_AREA_ID</t>
+  </si>
+  <si>
+    <t>CB_AREA_NM</t>
+  </si>
+  <si>
+    <t>am.CB_AREA_NM</t>
+  </si>
+  <si>
+    <t>CRT_TM</t>
+  </si>
+  <si>
+    <t>TIMESTAMP</t>
+  </si>
+  <si>
+    <t>CURRENT_TIMESTAMP()</t>
+  </si>
+  <si>
+    <t>EFF_FM_DT</t>
+  </si>
+  <si>
+    <t>DATE</t>
+  </si>
+  <si>
+    <t>constant</t>
+  </si>
+  <si>
+    <t>NULL</t>
+  </si>
+  <si>
+    <t>EFF_TO_DT</t>
+  </si>
+  <si>
+    <t>bm.PARENT_BRANCH_CODE</t>
+  </si>
+  <si>
+    <t>START_WK_DT</t>
+  </si>
+  <si>
+    <t>hub.source_event_date</t>
+  </si>
+  <si>
+    <t>OU_ADR</t>
+  </si>
+  <si>
+    <t>bm.ADDRESS</t>
+  </si>
+  <si>
+    <t>OU_PH</t>
+  </si>
+  <si>
+    <t>bm.PHONE_NUMBER</t>
+  </si>
+  <si>
+    <t>working_day — VIEW
+JOIN SCHEMA — WORKING_DAY</t>
+  </si>
+  <si>
+    <t>v_from_dt AS (
+    SELECT 
+        D.msr_prd_id                                                          AS DATA_DT,
+        DATE_FORMAT(
+            MAX(TO_DATE(CAST(B.msr_prd_id AS STRING), 'yyyyMMdd')) + INTERVAL 1 DAY,
+            'yyyyMMdd'
+        )                                                                     AS FROM_DT,
+        MAX(TO_DATE(CAST(B.msr_prd_id AS STRING), 'yyyyMMdd')) + INTERVAL 1 DAY AS FROM_DATE_DT
+    FROM ocb_datavault_pilotcloud_cleaned.business_vault.calendar D
+    LEFT JOIN ocb_datavault_pilotcloud_cleaned.business_vault.calendar B
+        ON D.msr_prd_id &gt; B.msr_prd_id
+        AND B.bsn_day_f = 1   -- B là ngày làm việc trước D
+    WHERE D.bsn_day_f = 1     -- D là ngày làm việc
+    GROUP BY D.msr_prd_id
+)</t>
+  </si>
+  <si>
+    <t>v_end_dt AS (
+    SELECT 
+        D.msr_prd_id                                                          AS DATA_DT,
+        DATE_FORMAT(
+            MIN(TO_DATE(CAST(E.msr_prd_id AS STRING), 'yyyyMMdd')) - INTERVAL 1 DAY,
+            'yyyyMMdd'
+        )                                                                     AS END_DT,
+        MIN(TO_DATE(CAST(E.msr_prd_id AS STRING), 'yyyyMMdd')) - INTERVAL 1 DAY AS END_DATE_DT
+    FROM ocb_datavault_pilotcloud_cleaned.business_vault.calendar D
+    LEFT JOIN ocb_datavault_pilotcloud_cleaned.business_vault.calendar E
+        ON D.msr_prd_id &lt; E.msr_prd_id
+        AND E.bsn_day_f = 1 
+    WHERE D.bsn_day_f = 1    
+    GROUP BY D.msr_prd_id
+)</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>JOIN</t>
+  </si>
+  <si>
+    <t>ON B.DATA_DT = E.DATA_DT</t>
+  </si>
+  <si>
+    <t>Cơ chế: lấy dữ liệu ngày mới (TRUNCATE xpng INSERT)</t>
+  </si>
+  <si>
+    <t>FIELD MAPPING — WORKING_DAY</t>
+  </si>
+  <si>
+    <t>Field (Output Col)</t>
+  </si>
+  <si>
+    <t>TransformType</t>
+  </si>
+  <si>
+    <t>working_day</t>
+  </si>
+  <si>
+    <t>DATA_DT</t>
+  </si>
+  <si>
+    <t>TRANSFORM</t>
+  </si>
+  <si>
+    <t>E.DATA_DT</t>
+  </si>
+  <si>
+    <t>FROM_DATE_DT</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>TO_DATE( CASE WHEN SUBSTR(B.FROM_DT,1,6) &lt; SUBSTR(CAST(B.DATA_DT AS STRING),1,6) OR SUBSTR(B.FROM_DT,7,2) = '01'
+            THEN CONCAT(SUBSTR(CAST(B.DATA_DT AS STRING),1,6),'01')
+            ELSE CAST(B.DATA_DT AS STRING)
+        END, 'yyyyMMdd') AS FROM_DATE_DT</t>
+  </si>
+  <si>
+    <t>FROM_DT</t>
+  </si>
+  <si>
+    <t>CONCAT(SUBSTR(CAST(B.DATA_DT AS STRING),1,6),'01')</t>
+  </si>
+  <si>
+    <t>END_DT</t>
+  </si>
+  <si>
+    <t>CAST(B.DATA_DT AS STRING)</t>
+  </si>
+  <si>
+    <t>END_DATE_DT</t>
+  </si>
+  <si>
+    <t>timestamp</t>
+  </si>
+  <si>
+    <t>END, 'yyyyMMdd') AS FROM_DATE_DT</t>
+  </si>
+  <si>
+    <t>BEGIN_OF_MONTH</t>
+  </si>
+  <si>
+    <t>CASE WHEN SUBSTR(B.FROM_DT,1,6) &lt; SUBSTR(CAST(B.DATA_DT AS STRING),1,6) OR SUBSTR(B.FROM_DT,7,2) = '01'</t>
+  </si>
+  <si>
+    <t>BEGIN_OF_MONTH_DATE</t>
+  </si>
+  <si>
+    <t>THEN CONCAT(SUBSTR(CAST(B.DATA_DT AS STRING),1,6),'01')</t>
+  </si>
+  <si>
+    <t>HOLIDAY — VIEW
+JOIN SCHEMA — HOLIDAY</t>
+  </si>
+  <si>
+    <t>calendar</t>
+  </si>
+  <si>
+    <t>FROM ocb_datavault_pilotcloud_cleaned.business_vault.calendar D
+WHERE D.bsn_day_f = 0    -- D là ngày nghỉ
+GROUP BY D.msr_prd_id
+ORDER BY D.msr_prd_id;</t>
+  </si>
+  <si>
+    <t>LEFT JOIN ocb_datavault_pilotcloud_cleaned.business_vault.calendar W
+    ON D.msr_prd_id &gt; W.msr_prd_id
+    AND W.bsn_day_f = 1   -- W là ngày làm việc</t>
+  </si>
+  <si>
+    <t>Cơ chế: lấy dữ liệu ngày mới (TRUNCATE THEN INSERT)</t>
+  </si>
+  <si>
+    <t>FIELD MAPPING — HOLIDAY</t>
+  </si>
+  <si>
+    <t>DATA_DATE_DT</t>
+  </si>
+  <si>
+    <t>TO_DATE(CAST(MAX(W.MSR_PRD_ID) AS STRING), 'yyyyMMdd')</t>
+  </si>
+  <si>
+    <t>HOLIDAY_DATE_DT</t>
+  </si>
+  <si>
+    <t>TO_DATE(CAST(D.MSR_PRD_ID AS STRING), 'yyyyMMdd')</t>
+  </si>
+  <si>
+    <t>MAX(W.MSR_PRD_ID)</t>
+  </si>
+  <si>
+    <t>HOLIDAY_DT</t>
+  </si>
+  <si>
+    <t>D.MSR_PRD_ID</t>
   </si>
 </sst>
 </file>
@@ -3238,7 +3118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="172">
+  <cellXfs count="171">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -3576,69 +3456,6 @@
     <xf numFmtId="0" fontId="1" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -3647,59 +3464,22 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="7" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="6"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="8"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3712,6 +3492,105 @@
     <xf numFmtId="0" fontId="29" fillId="13" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="29" fillId="14" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="29" fillId="15" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="6"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="8"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -4051,658 +3930,584 @@
   <dimension ref="A1:Y42"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="2" style="144" customWidth="1"/>
-    <col min="2" max="5" width="14" style="144" customWidth="1"/>
-    <col min="6" max="6" width="10.28515625" style="144" customWidth="1"/>
-    <col min="7" max="10" width="14" style="144" customWidth="1"/>
-    <col min="11" max="11" width="5" style="144" customWidth="1"/>
-    <col min="12" max="15" width="16" style="144" customWidth="1"/>
-    <col min="16" max="16" width="5" style="144" customWidth="1"/>
-    <col min="17" max="20" width="16" style="144" customWidth="1"/>
-    <col min="21" max="21" width="4" style="144" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="144"/>
+    <col min="1" max="1" width="2" style="121" customWidth="1"/>
+    <col min="2" max="5" width="14" style="121" customWidth="1"/>
+    <col min="6" max="6" width="10.28515625" style="121" customWidth="1"/>
+    <col min="7" max="10" width="14" style="121" customWidth="1"/>
+    <col min="11" max="11" width="5" style="121" customWidth="1"/>
+    <col min="12" max="15" width="16" style="121" customWidth="1"/>
+    <col min="16" max="16" width="5" style="121" customWidth="1"/>
+    <col min="17" max="20" width="16" style="121" customWidth="1"/>
+    <col min="21" max="21" width="4" style="121" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="121"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="30" customHeight="1">
-      <c r="A1" s="143" t="s">
+      <c r="A1" s="139" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="143"/>
-      <c r="G1" s="143"/>
-      <c r="H1" s="143"/>
-      <c r="I1" s="143"/>
-      <c r="J1" s="143"/>
-      <c r="K1" s="143"/>
-      <c r="L1" s="143"/>
-      <c r="M1" s="143"/>
-      <c r="N1" s="143"/>
-      <c r="O1" s="143"/>
-      <c r="P1" s="143"/>
-      <c r="Q1" s="143"/>
-      <c r="R1" s="143"/>
-      <c r="S1" s="143"/>
-      <c r="T1" s="143"/>
-      <c r="U1" s="143"/>
-      <c r="V1" s="143"/>
-      <c r="W1" s="143"/>
-      <c r="X1" s="143"/>
-      <c r="Y1" s="143"/>
+      <c r="B1" s="139"/>
+      <c r="C1" s="139"/>
+      <c r="D1" s="139"/>
+      <c r="E1" s="139"/>
+      <c r="F1" s="139"/>
+      <c r="G1" s="139"/>
+      <c r="H1" s="139"/>
+      <c r="I1" s="139"/>
+      <c r="J1" s="139"/>
+      <c r="K1" s="139"/>
+      <c r="L1" s="139"/>
+      <c r="M1" s="139"/>
+      <c r="N1" s="139"/>
+      <c r="O1" s="139"/>
+      <c r="P1" s="139"/>
+      <c r="Q1" s="139"/>
+      <c r="R1" s="139"/>
+      <c r="S1" s="139"/>
+      <c r="T1" s="139"/>
+      <c r="U1" s="139"/>
+      <c r="V1" s="139"/>
+      <c r="W1" s="139"/>
+      <c r="X1" s="139"/>
+      <c r="Y1" s="139"/>
     </row>
     <row r="2" spans="1:25" ht="6" customHeight="1"/>
     <row r="3" spans="1:25" ht="22.15" customHeight="1">
-      <c r="B3" s="145" t="s">
+      <c r="B3" s="142" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="145"/>
-      <c r="D3" s="145"/>
-      <c r="E3" s="145"/>
-      <c r="F3" s="146"/>
-      <c r="G3" s="147" t="s">
+      <c r="C3" s="142"/>
+      <c r="D3" s="142"/>
+      <c r="E3" s="142"/>
+      <c r="G3" s="144" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="171"/>
-      <c r="I3" s="171"/>
-      <c r="J3" s="171"/>
-      <c r="K3" s="146"/>
-      <c r="L3" s="148" t="s">
+      <c r="H3" s="170"/>
+      <c r="I3" s="170"/>
+      <c r="J3" s="170"/>
+      <c r="L3" s="138" t="s">
         <v>3</v>
       </c>
-      <c r="M3" s="171"/>
-      <c r="N3" s="171"/>
-      <c r="O3" s="171"/>
-      <c r="P3" s="146"/>
-      <c r="Q3" s="148" t="s">
+      <c r="M3" s="170"/>
+      <c r="N3" s="170"/>
+      <c r="O3" s="170"/>
+      <c r="Q3" s="138" t="s">
         <v>4</v>
       </c>
-      <c r="R3" s="171"/>
-      <c r="S3" s="171"/>
-      <c r="T3" s="171"/>
-      <c r="U3" s="146"/>
-      <c r="V3" s="148" t="s">
+      <c r="R3" s="170"/>
+      <c r="S3" s="170"/>
+      <c r="T3" s="170"/>
+      <c r="V3" s="138" t="s">
         <v>5</v>
       </c>
-      <c r="W3" s="171"/>
-      <c r="X3" s="171"/>
-      <c r="Y3" s="171"/>
+      <c r="W3" s="170"/>
+      <c r="X3" s="170"/>
+      <c r="Y3" s="170"/>
     </row>
     <row r="4" spans="1:25" ht="11.45" customHeight="1">
-      <c r="B4" s="149"/>
-      <c r="C4" s="149"/>
-      <c r="D4" s="149"/>
-      <c r="E4" s="149"/>
-      <c r="F4" s="146"/>
-      <c r="G4" s="150"/>
-      <c r="H4" s="150"/>
-      <c r="I4" s="150"/>
-      <c r="J4" s="150"/>
-      <c r="K4" s="146"/>
-      <c r="L4" s="151"/>
-      <c r="M4" s="151"/>
-      <c r="N4" s="151"/>
-      <c r="O4" s="151"/>
-      <c r="P4" s="146"/>
-      <c r="U4" s="146"/>
+      <c r="B4" s="122"/>
+      <c r="C4" s="122"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="122"/>
+      <c r="G4" s="123"/>
+      <c r="H4" s="123"/>
+      <c r="I4" s="123"/>
+      <c r="J4" s="123"/>
+      <c r="L4" s="124"/>
+      <c r="M4" s="124"/>
+      <c r="N4" s="124"/>
+      <c r="O4" s="124"/>
     </row>
     <row r="5" spans="1:25" ht="19.5" customHeight="1">
-      <c r="B5" s="152" t="s">
+      <c r="B5" s="141" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="152"/>
-      <c r="D5" s="152"/>
-      <c r="E5" s="152"/>
-      <c r="F5" s="146"/>
-      <c r="G5" s="153" t="s">
+      <c r="C5" s="141"/>
+      <c r="D5" s="141"/>
+      <c r="E5" s="141"/>
+      <c r="G5" s="145" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="171"/>
-      <c r="I5" s="171"/>
-      <c r="J5" s="171"/>
-      <c r="K5" s="146"/>
-      <c r="L5" s="154" t="s">
+      <c r="H5" s="170"/>
+      <c r="I5" s="170"/>
+      <c r="J5" s="170"/>
+      <c r="L5" s="146" t="s">
         <v>8</v>
       </c>
-      <c r="M5" s="154"/>
-      <c r="N5" s="154"/>
-      <c r="O5" s="154"/>
-      <c r="P5" s="146"/>
-      <c r="Q5" s="155" t="s">
+      <c r="M5" s="146"/>
+      <c r="N5" s="146"/>
+      <c r="O5" s="146"/>
+      <c r="Q5" s="140" t="s">
         <v>9</v>
       </c>
-      <c r="R5" s="155"/>
-      <c r="S5" s="155"/>
-      <c r="T5" s="155"/>
-      <c r="U5" s="146"/>
+      <c r="R5" s="140"/>
+      <c r="S5" s="140"/>
+      <c r="T5" s="140"/>
     </row>
     <row r="6" spans="1:25" ht="19.899999999999999" customHeight="1">
-      <c r="B6" s="152"/>
-      <c r="C6" s="152"/>
-      <c r="D6" s="152"/>
-      <c r="E6" s="152"/>
-      <c r="F6" s="156"/>
-      <c r="G6" s="171"/>
-      <c r="H6" s="171"/>
-      <c r="I6" s="171"/>
-      <c r="J6" s="171"/>
-      <c r="K6" s="157" t="s">
+      <c r="B6" s="141"/>
+      <c r="C6" s="141"/>
+      <c r="D6" s="141"/>
+      <c r="E6" s="141"/>
+      <c r="F6" s="125"/>
+      <c r="G6" s="170"/>
+      <c r="H6" s="170"/>
+      <c r="I6" s="170"/>
+      <c r="J6" s="170"/>
+      <c r="K6" s="126" t="s">
         <v>10</v>
       </c>
-      <c r="L6" s="154"/>
-      <c r="M6" s="154"/>
-      <c r="N6" s="154"/>
-      <c r="O6" s="154"/>
-      <c r="P6" s="157" t="s">
+      <c r="L6" s="146"/>
+      <c r="M6" s="146"/>
+      <c r="N6" s="146"/>
+      <c r="O6" s="146"/>
+      <c r="P6" s="126" t="s">
         <v>10</v>
       </c>
-      <c r="Q6" s="155"/>
-      <c r="R6" s="155"/>
-      <c r="S6" s="155"/>
-      <c r="T6" s="155"/>
-      <c r="U6" s="157"/>
+      <c r="Q6" s="140"/>
+      <c r="R6" s="140"/>
+      <c r="S6" s="140"/>
+      <c r="T6" s="140"/>
+      <c r="U6" s="126"/>
     </row>
     <row r="7" spans="1:25" ht="19.899999999999999" customHeight="1">
-      <c r="B7" s="152"/>
-      <c r="C7" s="152"/>
-      <c r="D7" s="152"/>
-      <c r="E7" s="152"/>
-      <c r="F7" s="146"/>
-      <c r="G7" s="171"/>
-      <c r="H7" s="171"/>
-      <c r="I7" s="171"/>
-      <c r="J7" s="171"/>
-      <c r="K7" s="146"/>
-      <c r="L7" s="154"/>
-      <c r="M7" s="154"/>
-      <c r="N7" s="154"/>
-      <c r="O7" s="154"/>
-      <c r="P7" s="146"/>
-      <c r="Q7" s="155"/>
-      <c r="R7" s="155"/>
-      <c r="S7" s="155"/>
-      <c r="T7" s="155"/>
-      <c r="U7" s="146"/>
+      <c r="B7" s="141"/>
+      <c r="C7" s="141"/>
+      <c r="D7" s="141"/>
+      <c r="E7" s="141"/>
+      <c r="G7" s="170"/>
+      <c r="H7" s="170"/>
+      <c r="I7" s="170"/>
+      <c r="J7" s="170"/>
+      <c r="L7" s="146"/>
+      <c r="M7" s="146"/>
+      <c r="N7" s="146"/>
+      <c r="O7" s="146"/>
+      <c r="Q7" s="140"/>
+      <c r="R7" s="140"/>
+      <c r="S7" s="140"/>
+      <c r="T7" s="140"/>
     </row>
     <row r="8" spans="1:25" ht="7.15" customHeight="1">
-      <c r="B8" s="152"/>
-      <c r="C8" s="152"/>
-      <c r="D8" s="152"/>
-      <c r="E8" s="152"/>
-      <c r="F8" s="146"/>
-      <c r="G8" s="171"/>
-      <c r="H8" s="171"/>
-      <c r="I8" s="171"/>
-      <c r="J8" s="171"/>
-      <c r="K8" s="146"/>
-      <c r="P8" s="146"/>
-      <c r="U8" s="146"/>
+      <c r="B8" s="141"/>
+      <c r="C8" s="141"/>
+      <c r="D8" s="141"/>
+      <c r="E8" s="141"/>
+      <c r="G8" s="170"/>
+      <c r="H8" s="170"/>
+      <c r="I8" s="170"/>
+      <c r="J8" s="170"/>
     </row>
     <row r="9" spans="1:25" ht="19.899999999999999" customHeight="1">
-      <c r="B9" s="152"/>
-      <c r="C9" s="152"/>
-      <c r="D9" s="152"/>
-      <c r="E9" s="152"/>
-      <c r="F9" s="146"/>
-      <c r="G9" s="171"/>
-      <c r="H9" s="171"/>
-      <c r="I9" s="171"/>
-      <c r="J9" s="171"/>
-      <c r="K9" s="146"/>
-      <c r="L9" s="154" t="s">
+      <c r="B9" s="141"/>
+      <c r="C9" s="141"/>
+      <c r="D9" s="141"/>
+      <c r="E9" s="141"/>
+      <c r="G9" s="170"/>
+      <c r="H9" s="170"/>
+      <c r="I9" s="170"/>
+      <c r="J9" s="170"/>
+      <c r="L9" s="146" t="s">
         <v>11</v>
       </c>
-      <c r="M9" s="154"/>
-      <c r="N9" s="154"/>
-      <c r="O9" s="154"/>
-      <c r="P9" s="146"/>
-      <c r="Q9" s="155" t="s">
+      <c r="M9" s="146"/>
+      <c r="N9" s="146"/>
+      <c r="O9" s="146"/>
+      <c r="Q9" s="140" t="s">
         <v>9</v>
       </c>
-      <c r="R9" s="155"/>
-      <c r="S9" s="155"/>
-      <c r="T9" s="155"/>
-      <c r="U9" s="146"/>
+      <c r="R9" s="140"/>
+      <c r="S9" s="140"/>
+      <c r="T9" s="140"/>
     </row>
     <row r="10" spans="1:25" ht="19.899999999999999" customHeight="1">
-      <c r="B10" s="152"/>
-      <c r="C10" s="152"/>
-      <c r="D10" s="152"/>
-      <c r="E10" s="152"/>
-      <c r="F10" s="146"/>
-      <c r="G10" s="171"/>
-      <c r="H10" s="171"/>
-      <c r="I10" s="171"/>
-      <c r="J10" s="171"/>
-      <c r="K10" s="157" t="s">
+      <c r="B10" s="141"/>
+      <c r="C10" s="141"/>
+      <c r="D10" s="141"/>
+      <c r="E10" s="141"/>
+      <c r="G10" s="170"/>
+      <c r="H10" s="170"/>
+      <c r="I10" s="170"/>
+      <c r="J10" s="170"/>
+      <c r="K10" s="126" t="s">
         <v>10</v>
       </c>
-      <c r="L10" s="154"/>
-      <c r="M10" s="154"/>
-      <c r="N10" s="154"/>
-      <c r="O10" s="154"/>
-      <c r="P10" s="157" t="s">
+      <c r="L10" s="146"/>
+      <c r="M10" s="146"/>
+      <c r="N10" s="146"/>
+      <c r="O10" s="146"/>
+      <c r="P10" s="126" t="s">
         <v>10</v>
       </c>
-      <c r="Q10" s="155"/>
-      <c r="R10" s="155"/>
-      <c r="S10" s="155"/>
-      <c r="T10" s="155"/>
-      <c r="U10" s="157"/>
+      <c r="Q10" s="140"/>
+      <c r="R10" s="140"/>
+      <c r="S10" s="140"/>
+      <c r="T10" s="140"/>
+      <c r="U10" s="126"/>
     </row>
     <row r="11" spans="1:25" ht="19.899999999999999" customHeight="1">
-      <c r="B11" s="152"/>
-      <c r="C11" s="152"/>
-      <c r="D11" s="152"/>
-      <c r="E11" s="152"/>
-      <c r="F11" s="146"/>
-      <c r="G11" s="171"/>
-      <c r="H11" s="171"/>
-      <c r="I11" s="171"/>
-      <c r="J11" s="171"/>
-      <c r="K11" s="146"/>
-      <c r="L11" s="154"/>
-      <c r="M11" s="154"/>
-      <c r="N11" s="154"/>
-      <c r="O11" s="154"/>
-      <c r="P11" s="146"/>
-      <c r="Q11" s="155"/>
-      <c r="R11" s="155"/>
-      <c r="S11" s="155"/>
-      <c r="T11" s="155"/>
-      <c r="U11" s="146"/>
+      <c r="B11" s="141"/>
+      <c r="C11" s="141"/>
+      <c r="D11" s="141"/>
+      <c r="E11" s="141"/>
+      <c r="G11" s="170"/>
+      <c r="H11" s="170"/>
+      <c r="I11" s="170"/>
+      <c r="J11" s="170"/>
+      <c r="L11" s="146"/>
+      <c r="M11" s="146"/>
+      <c r="N11" s="146"/>
+      <c r="O11" s="146"/>
+      <c r="Q11" s="140"/>
+      <c r="R11" s="140"/>
+      <c r="S11" s="140"/>
+      <c r="T11" s="140"/>
     </row>
     <row r="12" spans="1:25" ht="7.15" customHeight="1">
-      <c r="B12" s="152"/>
-      <c r="C12" s="152"/>
-      <c r="D12" s="152"/>
-      <c r="E12" s="152"/>
-      <c r="F12" s="146"/>
-      <c r="G12" s="171"/>
-      <c r="H12" s="171"/>
-      <c r="I12" s="171"/>
-      <c r="J12" s="171"/>
-      <c r="K12" s="146"/>
-      <c r="P12" s="146"/>
-      <c r="U12" s="146"/>
+      <c r="B12" s="141"/>
+      <c r="C12" s="141"/>
+      <c r="D12" s="141"/>
+      <c r="E12" s="141"/>
+      <c r="G12" s="170"/>
+      <c r="H12" s="170"/>
+      <c r="I12" s="170"/>
+      <c r="J12" s="170"/>
     </row>
     <row r="13" spans="1:25" ht="19.899999999999999" customHeight="1">
-      <c r="B13" s="152"/>
-      <c r="C13" s="152"/>
-      <c r="D13" s="152"/>
-      <c r="E13" s="152"/>
-      <c r="F13" s="146"/>
-      <c r="G13" s="171"/>
-      <c r="H13" s="171"/>
-      <c r="I13" s="171"/>
-      <c r="J13" s="171"/>
-      <c r="K13" s="146"/>
-      <c r="L13" s="154" t="s">
+      <c r="B13" s="141"/>
+      <c r="C13" s="141"/>
+      <c r="D13" s="141"/>
+      <c r="E13" s="141"/>
+      <c r="G13" s="170"/>
+      <c r="H13" s="170"/>
+      <c r="I13" s="170"/>
+      <c r="J13" s="170"/>
+      <c r="L13" s="146" t="s">
         <v>12</v>
       </c>
-      <c r="M13" s="154"/>
-      <c r="N13" s="154"/>
-      <c r="O13" s="154"/>
-      <c r="P13" s="146"/>
-      <c r="Q13" s="158" t="s">
+      <c r="M13" s="146"/>
+      <c r="N13" s="146"/>
+      <c r="O13" s="146"/>
+      <c r="Q13" s="143" t="s">
         <v>13</v>
       </c>
-      <c r="R13" s="158"/>
-      <c r="S13" s="158"/>
-      <c r="T13" s="158"/>
-      <c r="U13" s="146"/>
+      <c r="R13" s="143"/>
+      <c r="S13" s="143"/>
+      <c r="T13" s="143"/>
     </row>
     <row r="14" spans="1:25" ht="19.899999999999999" customHeight="1">
-      <c r="B14" s="152"/>
-      <c r="C14" s="152"/>
-      <c r="D14" s="152"/>
-      <c r="E14" s="152"/>
-      <c r="F14" s="146"/>
-      <c r="G14" s="171"/>
-      <c r="H14" s="171"/>
-      <c r="I14" s="171"/>
-      <c r="J14" s="171"/>
-      <c r="K14" s="157" t="s">
+      <c r="B14" s="141"/>
+      <c r="C14" s="141"/>
+      <c r="D14" s="141"/>
+      <c r="E14" s="141"/>
+      <c r="G14" s="170"/>
+      <c r="H14" s="170"/>
+      <c r="I14" s="170"/>
+      <c r="J14" s="170"/>
+      <c r="K14" s="126" t="s">
         <v>10</v>
       </c>
-      <c r="L14" s="154"/>
-      <c r="M14" s="154"/>
-      <c r="N14" s="154"/>
-      <c r="O14" s="154"/>
-      <c r="P14" s="157"/>
-      <c r="Q14" s="158"/>
-      <c r="R14" s="158"/>
-      <c r="S14" s="158"/>
-      <c r="T14" s="158"/>
-      <c r="U14" s="157"/>
+      <c r="L14" s="146"/>
+      <c r="M14" s="146"/>
+      <c r="N14" s="146"/>
+      <c r="O14" s="146"/>
+      <c r="P14" s="126"/>
+      <c r="Q14" s="143"/>
+      <c r="R14" s="143"/>
+      <c r="S14" s="143"/>
+      <c r="T14" s="143"/>
+      <c r="U14" s="126"/>
     </row>
     <row r="15" spans="1:25" ht="153" customHeight="1">
-      <c r="B15" s="152"/>
-      <c r="C15" s="152"/>
-      <c r="D15" s="152"/>
-      <c r="E15" s="152"/>
-      <c r="F15" s="146"/>
-      <c r="G15" s="171"/>
-      <c r="H15" s="171"/>
-      <c r="I15" s="171"/>
-      <c r="J15" s="171"/>
-      <c r="K15" s="146"/>
-      <c r="L15" s="154"/>
-      <c r="M15" s="154"/>
-      <c r="N15" s="154"/>
-      <c r="O15" s="154"/>
-      <c r="P15" s="159" t="s">
+      <c r="B15" s="141"/>
+      <c r="C15" s="141"/>
+      <c r="D15" s="141"/>
+      <c r="E15" s="141"/>
+      <c r="G15" s="170"/>
+      <c r="H15" s="170"/>
+      <c r="I15" s="170"/>
+      <c r="J15" s="170"/>
+      <c r="L15" s="146"/>
+      <c r="M15" s="146"/>
+      <c r="N15" s="146"/>
+      <c r="O15" s="146"/>
+      <c r="P15" s="127" t="s">
         <v>14</v>
       </c>
-      <c r="Q15" s="158"/>
-      <c r="R15" s="158"/>
-      <c r="S15" s="158"/>
-      <c r="T15" s="158"/>
-      <c r="U15" s="159"/>
+      <c r="Q15" s="143"/>
+      <c r="R15" s="143"/>
+      <c r="S15" s="143"/>
+      <c r="T15" s="143"/>
+      <c r="U15" s="127"/>
     </row>
     <row r="16" spans="1:25" ht="15.75" customHeight="1">
-      <c r="B16" s="152"/>
-      <c r="C16" s="152"/>
-      <c r="D16" s="152"/>
-      <c r="E16" s="152"/>
-      <c r="F16" s="156" t="s">
+      <c r="B16" s="141"/>
+      <c r="C16" s="141"/>
+      <c r="D16" s="141"/>
+      <c r="E16" s="141"/>
+      <c r="F16" s="125" t="s">
         <v>10</v>
       </c>
-      <c r="G16" s="171"/>
-      <c r="H16" s="171"/>
-      <c r="I16" s="171"/>
-      <c r="J16" s="171"/>
-      <c r="K16" s="146"/>
-      <c r="P16" s="146"/>
-      <c r="U16" s="146"/>
+      <c r="G16" s="170"/>
+      <c r="H16" s="170"/>
+      <c r="I16" s="170"/>
+      <c r="J16" s="170"/>
     </row>
     <row r="17" spans="2:25" ht="19.899999999999999" customHeight="1">
-      <c r="B17" s="152"/>
-      <c r="C17" s="152"/>
-      <c r="D17" s="152"/>
-      <c r="E17" s="152"/>
-      <c r="F17" s="146"/>
-      <c r="G17" s="171"/>
-      <c r="H17" s="171"/>
-      <c r="I17" s="171"/>
-      <c r="J17" s="171"/>
-      <c r="K17" s="146"/>
-      <c r="L17" s="160" t="s">
+      <c r="B17" s="141"/>
+      <c r="C17" s="141"/>
+      <c r="D17" s="141"/>
+      <c r="E17" s="141"/>
+      <c r="G17" s="170"/>
+      <c r="H17" s="170"/>
+      <c r="I17" s="170"/>
+      <c r="J17" s="170"/>
+      <c r="L17" s="147" t="s">
         <v>15</v>
       </c>
-      <c r="M17" s="160"/>
-      <c r="N17" s="160"/>
-      <c r="O17" s="160"/>
-      <c r="P17" s="146"/>
-      <c r="U17" s="146"/>
+      <c r="M17" s="147"/>
+      <c r="N17" s="147"/>
+      <c r="O17" s="147"/>
     </row>
     <row r="18" spans="2:25" ht="19.899999999999999" customHeight="1">
-      <c r="B18" s="152"/>
-      <c r="C18" s="152"/>
-      <c r="D18" s="152"/>
-      <c r="E18" s="152"/>
-      <c r="F18" s="146"/>
-      <c r="G18" s="171"/>
-      <c r="H18" s="171"/>
-      <c r="I18" s="171"/>
-      <c r="J18" s="171"/>
-      <c r="K18" s="157" t="s">
+      <c r="B18" s="141"/>
+      <c r="C18" s="141"/>
+      <c r="D18" s="141"/>
+      <c r="E18" s="141"/>
+      <c r="G18" s="170"/>
+      <c r="H18" s="170"/>
+      <c r="I18" s="170"/>
+      <c r="J18" s="170"/>
+      <c r="K18" s="126" t="s">
         <v>10</v>
       </c>
-      <c r="L18" s="160"/>
-      <c r="M18" s="160"/>
-      <c r="N18" s="160"/>
-      <c r="O18" s="160"/>
-      <c r="P18" s="157"/>
-      <c r="U18" s="157"/>
+      <c r="L18" s="147"/>
+      <c r="M18" s="147"/>
+      <c r="N18" s="147"/>
+      <c r="O18" s="147"/>
+      <c r="P18" s="126"/>
+      <c r="U18" s="126"/>
     </row>
     <row r="19" spans="2:25" ht="19.899999999999999" customHeight="1">
-      <c r="B19" s="152"/>
-      <c r="C19" s="152"/>
-      <c r="D19" s="152"/>
-      <c r="E19" s="152"/>
-      <c r="F19" s="146"/>
-      <c r="G19" s="171"/>
-      <c r="H19" s="171"/>
-      <c r="I19" s="171"/>
-      <c r="J19" s="171"/>
-      <c r="K19" s="146"/>
-      <c r="L19" s="160"/>
-      <c r="M19" s="160"/>
-      <c r="N19" s="160"/>
-      <c r="O19" s="160"/>
-      <c r="P19" s="146"/>
-      <c r="U19" s="146"/>
+      <c r="B19" s="141"/>
+      <c r="C19" s="141"/>
+      <c r="D19" s="141"/>
+      <c r="E19" s="141"/>
+      <c r="G19" s="170"/>
+      <c r="H19" s="170"/>
+      <c r="I19" s="170"/>
+      <c r="J19" s="170"/>
+      <c r="L19" s="147"/>
+      <c r="M19" s="147"/>
+      <c r="N19" s="147"/>
+      <c r="O19" s="147"/>
     </row>
     <row r="20" spans="2:25" ht="10.15" customHeight="1">
-      <c r="B20" s="152"/>
-      <c r="C20" s="152"/>
-      <c r="D20" s="152"/>
-      <c r="E20" s="152"/>
-      <c r="F20" s="146"/>
-      <c r="G20" s="171"/>
-      <c r="H20" s="171"/>
-      <c r="I20" s="171"/>
-      <c r="J20" s="171"/>
-      <c r="K20" s="146"/>
-      <c r="P20" s="146"/>
-      <c r="U20" s="146"/>
+      <c r="B20" s="141"/>
+      <c r="C20" s="141"/>
+      <c r="D20" s="141"/>
+      <c r="E20" s="141"/>
+      <c r="G20" s="170"/>
+      <c r="H20" s="170"/>
+      <c r="I20" s="170"/>
+      <c r="J20" s="170"/>
     </row>
     <row r="21" spans="2:25" ht="19.899999999999999" customHeight="1">
-      <c r="B21" s="152"/>
-      <c r="C21" s="152"/>
-      <c r="D21" s="152"/>
-      <c r="E21" s="152"/>
-      <c r="F21" s="146"/>
-      <c r="G21" s="171"/>
-      <c r="H21" s="171"/>
-      <c r="I21" s="171"/>
-      <c r="J21" s="171"/>
-      <c r="K21" s="146"/>
-      <c r="L21" s="154" t="s">
+      <c r="B21" s="141"/>
+      <c r="C21" s="141"/>
+      <c r="D21" s="141"/>
+      <c r="E21" s="141"/>
+      <c r="G21" s="170"/>
+      <c r="H21" s="170"/>
+      <c r="I21" s="170"/>
+      <c r="J21" s="170"/>
+      <c r="L21" s="146" t="s">
         <v>16</v>
       </c>
-      <c r="M21" s="154"/>
-      <c r="N21" s="154"/>
-      <c r="O21" s="154"/>
-      <c r="P21" s="146"/>
-      <c r="Q21" s="154" t="s">
+      <c r="M21" s="146"/>
+      <c r="N21" s="146"/>
+      <c r="O21" s="146"/>
+      <c r="Q21" s="146" t="s">
         <v>17</v>
       </c>
-      <c r="R21" s="154"/>
-      <c r="S21" s="154"/>
-      <c r="T21" s="154"/>
-      <c r="U21" s="146"/>
-      <c r="V21" s="161" t="s">
+      <c r="R21" s="146"/>
+      <c r="S21" s="146"/>
+      <c r="T21" s="146"/>
+      <c r="V21" s="148" t="s">
         <v>18</v>
       </c>
-      <c r="W21" s="161"/>
-      <c r="X21" s="161"/>
-      <c r="Y21" s="161"/>
+      <c r="W21" s="148"/>
+      <c r="X21" s="148"/>
+      <c r="Y21" s="148"/>
     </row>
     <row r="22" spans="2:25" ht="19.899999999999999" customHeight="1">
-      <c r="B22" s="152"/>
-      <c r="C22" s="152"/>
-      <c r="D22" s="152"/>
-      <c r="E22" s="152"/>
-      <c r="F22" s="146"/>
-      <c r="G22" s="171"/>
-      <c r="H22" s="171"/>
-      <c r="I22" s="171"/>
-      <c r="J22" s="171"/>
-      <c r="K22" s="157" t="s">
+      <c r="B22" s="141"/>
+      <c r="C22" s="141"/>
+      <c r="D22" s="141"/>
+      <c r="E22" s="141"/>
+      <c r="G22" s="170"/>
+      <c r="H22" s="170"/>
+      <c r="I22" s="170"/>
+      <c r="J22" s="170"/>
+      <c r="K22" s="126" t="s">
         <v>10</v>
       </c>
-      <c r="L22" s="154"/>
-      <c r="M22" s="154"/>
-      <c r="N22" s="154"/>
-      <c r="O22" s="154"/>
-      <c r="P22" s="157"/>
-      <c r="Q22" s="154"/>
-      <c r="R22" s="154"/>
-      <c r="S22" s="154"/>
-      <c r="T22" s="154"/>
-      <c r="U22" s="157"/>
-      <c r="V22" s="161"/>
-      <c r="W22" s="161"/>
-      <c r="X22" s="161"/>
-      <c r="Y22" s="161"/>
+      <c r="L22" s="146"/>
+      <c r="M22" s="146"/>
+      <c r="N22" s="146"/>
+      <c r="O22" s="146"/>
+      <c r="P22" s="126"/>
+      <c r="Q22" s="146"/>
+      <c r="R22" s="146"/>
+      <c r="S22" s="146"/>
+      <c r="T22" s="146"/>
+      <c r="U22" s="126"/>
+      <c r="V22" s="148"/>
+      <c r="W22" s="148"/>
+      <c r="X22" s="148"/>
+      <c r="Y22" s="148"/>
     </row>
     <row r="23" spans="2:25" ht="42.75" customHeight="1">
-      <c r="B23" s="152"/>
-      <c r="C23" s="152"/>
-      <c r="D23" s="152"/>
-      <c r="E23" s="152"/>
-      <c r="F23" s="146"/>
-      <c r="G23" s="171"/>
-      <c r="H23" s="171"/>
-      <c r="I23" s="171"/>
-      <c r="J23" s="171"/>
-      <c r="K23" s="146"/>
-      <c r="L23" s="154"/>
-      <c r="M23" s="154"/>
-      <c r="N23" s="154"/>
-      <c r="O23" s="154"/>
-      <c r="P23" s="162" t="s">
+      <c r="B23" s="141"/>
+      <c r="C23" s="141"/>
+      <c r="D23" s="141"/>
+      <c r="E23" s="141"/>
+      <c r="G23" s="170"/>
+      <c r="H23" s="170"/>
+      <c r="I23" s="170"/>
+      <c r="J23" s="170"/>
+      <c r="L23" s="146"/>
+      <c r="M23" s="146"/>
+      <c r="N23" s="146"/>
+      <c r="O23" s="146"/>
+      <c r="P23" s="128" t="s">
         <v>10</v>
       </c>
-      <c r="Q23" s="154"/>
-      <c r="R23" s="154"/>
-      <c r="S23" s="154"/>
-      <c r="T23" s="154"/>
-      <c r="U23" s="162" t="s">
+      <c r="Q23" s="146"/>
+      <c r="R23" s="146"/>
+      <c r="S23" s="146"/>
+      <c r="T23" s="146"/>
+      <c r="U23" s="128" t="s">
         <v>10</v>
       </c>
-      <c r="V23" s="161"/>
-      <c r="W23" s="161"/>
-      <c r="X23" s="161"/>
-      <c r="Y23" s="161"/>
+      <c r="V23" s="148"/>
+      <c r="W23" s="148"/>
+      <c r="X23" s="148"/>
+      <c r="Y23" s="148"/>
     </row>
     <row r="24" spans="2:25" ht="7.9" customHeight="1">
-      <c r="B24" s="152"/>
-      <c r="C24" s="152"/>
-      <c r="D24" s="152"/>
-      <c r="E24" s="152"/>
-      <c r="F24" s="146"/>
-      <c r="G24" s="171"/>
-      <c r="H24" s="171"/>
-      <c r="I24" s="171"/>
-      <c r="J24" s="171"/>
-      <c r="K24" s="146"/>
-      <c r="P24" s="146"/>
-      <c r="U24" s="146"/>
+      <c r="B24" s="141"/>
+      <c r="C24" s="141"/>
+      <c r="D24" s="141"/>
+      <c r="E24" s="141"/>
+      <c r="G24" s="170"/>
+      <c r="H24" s="170"/>
+      <c r="I24" s="170"/>
+      <c r="J24" s="170"/>
     </row>
     <row r="25" spans="2:25" ht="19.899999999999999" customHeight="1">
-      <c r="B25" s="152"/>
-      <c r="C25" s="152"/>
-      <c r="D25" s="152"/>
-      <c r="E25" s="152"/>
-      <c r="F25" s="146"/>
-      <c r="G25" s="171"/>
-      <c r="H25" s="171"/>
-      <c r="I25" s="171"/>
-      <c r="J25" s="171"/>
-      <c r="K25" s="146"/>
-      <c r="L25" s="154" t="s">
+      <c r="B25" s="141"/>
+      <c r="C25" s="141"/>
+      <c r="D25" s="141"/>
+      <c r="E25" s="141"/>
+      <c r="G25" s="170"/>
+      <c r="H25" s="170"/>
+      <c r="I25" s="170"/>
+      <c r="J25" s="170"/>
+      <c r="L25" s="146" t="s">
         <v>19</v>
       </c>
-      <c r="M25" s="154"/>
-      <c r="N25" s="154"/>
-      <c r="O25" s="154"/>
-      <c r="P25" s="146"/>
-      <c r="Q25" s="158" t="s">
+      <c r="M25" s="146"/>
+      <c r="N25" s="146"/>
+      <c r="O25" s="146"/>
+      <c r="Q25" s="143" t="s">
         <v>20</v>
       </c>
-      <c r="R25" s="158"/>
-      <c r="S25" s="158"/>
-      <c r="T25" s="158"/>
-      <c r="U25" s="146"/>
+      <c r="R25" s="143"/>
+      <c r="S25" s="143"/>
+      <c r="T25" s="143"/>
     </row>
     <row r="26" spans="2:25" ht="19.899999999999999" customHeight="1">
-      <c r="B26" s="152"/>
-      <c r="C26" s="152"/>
-      <c r="D26" s="152"/>
-      <c r="E26" s="152"/>
-      <c r="F26" s="146"/>
-      <c r="G26" s="171"/>
-      <c r="H26" s="171"/>
-      <c r="I26" s="171"/>
-      <c r="J26" s="171"/>
-      <c r="K26" s="157" t="s">
+      <c r="B26" s="141"/>
+      <c r="C26" s="141"/>
+      <c r="D26" s="141"/>
+      <c r="E26" s="141"/>
+      <c r="G26" s="170"/>
+      <c r="H26" s="170"/>
+      <c r="I26" s="170"/>
+      <c r="J26" s="170"/>
+      <c r="K26" s="126" t="s">
         <v>10</v>
       </c>
-      <c r="L26" s="154"/>
-      <c r="M26" s="154"/>
-      <c r="N26" s="154"/>
-      <c r="O26" s="154"/>
-      <c r="P26" s="157"/>
-      <c r="Q26" s="158"/>
-      <c r="R26" s="158"/>
-      <c r="S26" s="158"/>
-      <c r="T26" s="158"/>
-      <c r="U26" s="157"/>
+      <c r="L26" s="146"/>
+      <c r="M26" s="146"/>
+      <c r="N26" s="146"/>
+      <c r="O26" s="146"/>
+      <c r="P26" s="126"/>
+      <c r="Q26" s="143"/>
+      <c r="R26" s="143"/>
+      <c r="S26" s="143"/>
+      <c r="T26" s="143"/>
+      <c r="U26" s="126"/>
     </row>
     <row r="27" spans="2:25" ht="93" customHeight="1">
-      <c r="B27" s="152"/>
-      <c r="C27" s="152"/>
-      <c r="D27" s="152"/>
-      <c r="E27" s="152"/>
-      <c r="F27" s="146"/>
-      <c r="G27" s="171"/>
-      <c r="H27" s="171"/>
-      <c r="I27" s="171"/>
-      <c r="J27" s="171"/>
-      <c r="K27" s="146"/>
-      <c r="L27" s="154"/>
-      <c r="M27" s="154"/>
-      <c r="N27" s="154"/>
-      <c r="O27" s="154"/>
-      <c r="P27" s="159" t="s">
+      <c r="B27" s="141"/>
+      <c r="C27" s="141"/>
+      <c r="D27" s="141"/>
+      <c r="E27" s="141"/>
+      <c r="G27" s="170"/>
+      <c r="H27" s="170"/>
+      <c r="I27" s="170"/>
+      <c r="J27" s="170"/>
+      <c r="L27" s="146"/>
+      <c r="M27" s="146"/>
+      <c r="N27" s="146"/>
+      <c r="O27" s="146"/>
+      <c r="P27" s="127" t="s">
         <v>21</v>
       </c>
-      <c r="Q27" s="158"/>
-      <c r="R27" s="158"/>
-      <c r="S27" s="158"/>
-      <c r="T27" s="158"/>
-      <c r="U27" s="159"/>
+      <c r="Q27" s="143"/>
+      <c r="R27" s="143"/>
+      <c r="S27" s="143"/>
+      <c r="T27" s="143"/>
+      <c r="U27" s="127"/>
     </row>
     <row r="29" spans="2:25"/>
     <row r="30" spans="2:25" ht="22.15" customHeight="1"/>
     <row r="31" spans="2:25" ht="22.15" customHeight="1"/>
     <row r="32" spans="2:25" ht="18" customHeight="1">
-      <c r="F32" s="163" t="s">
+      <c r="F32" s="129" t="s">
         <v>22</v>
       </c>
-      <c r="G32" s="164"/>
+      <c r="G32" s="130"/>
     </row>
     <row r="33" spans="6:7" ht="24" customHeight="1">
-      <c r="F33" s="165"/>
-      <c r="G33" s="166" t="s">
+      <c r="F33" s="131"/>
+      <c r="G33" s="132" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="34" spans="6:7" ht="24" customHeight="1">
-      <c r="F34" s="167"/>
-      <c r="G34" s="166" t="s">
+      <c r="F34" s="133"/>
+      <c r="G34" s="132" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="35" spans="6:7" ht="24" customHeight="1">
-      <c r="F35" s="168"/>
-      <c r="G35" s="166" t="s">
+      <c r="F35" s="134"/>
+      <c r="G35" s="132" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="36" spans="6:7" ht="24" customHeight="1">
-      <c r="F36" s="169"/>
-      <c r="G36" s="166" t="s">
+      <c r="F36" s="135"/>
+      <c r="G36" s="132" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="37" spans="6:7" ht="23.25" customHeight="1">
-      <c r="F37" s="170"/>
-      <c r="G37" s="166" t="s">
+      <c r="F37" s="136"/>
+      <c r="G37" s="132" t="s">
         <v>27</v>
       </c>
     </row>
@@ -4713,6 +4518,10 @@
     <row r="42" spans="6:7" ht="33.6" customHeight="1"/>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="L25:O27"/>
+    <mergeCell ref="Q21:T23"/>
+    <mergeCell ref="Q13:T15"/>
+    <mergeCell ref="V21:Y23"/>
     <mergeCell ref="V3:Y3"/>
     <mergeCell ref="A1:Y1"/>
     <mergeCell ref="Q5:T7"/>
@@ -4729,10 +4538,6 @@
     <mergeCell ref="L13:O15"/>
     <mergeCell ref="L17:O19"/>
     <mergeCell ref="L21:O23"/>
-    <mergeCell ref="L25:O27"/>
-    <mergeCell ref="Q21:T23"/>
-    <mergeCell ref="Q13:T15"/>
-    <mergeCell ref="V21:Y23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -4744,479 +4549,479 @@
   <dimension ref="A1:C116"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="15.28515625" style="139" customWidth="1"/>
-    <col min="2" max="2" width="22.28515625" style="139" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.42578125" style="139" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="139"/>
+    <col min="1" max="1" width="15.28515625" style="118" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" style="118" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="216.28515625" style="118" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="118"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A1" s="138"/>
+      <c r="A1" s="117"/>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="140" t="s">
+      <c r="A2" s="119" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="140" t="s">
+      <c r="B2" s="119" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="140" t="s">
+      <c r="C2" s="119" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="139" t="s">
+      <c r="A3" s="118" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="139" t="s">
+      <c r="B3" s="118" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="139" t="s">
+      <c r="C3" s="118" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="139" t="s">
+      <c r="A4" s="118" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="139" t="s">
+      <c r="B4" s="118" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="139" t="s">
+      <c r="C4" s="118" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="139" t="s">
+      <c r="A5" s="118" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="139" t="s">
+      <c r="B5" s="118" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="139" t="s">
+      <c r="C5" s="118" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="139" t="s">
+      <c r="A6" s="118" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="139" t="s">
+      <c r="B6" s="118" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="139" t="s">
+      <c r="C6" s="118" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="139" t="s">
+      <c r="A7" s="118" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="139" t="s">
+      <c r="B7" s="118" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="139" t="s">
+      <c r="C7" s="118" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="139" t="s">
+      <c r="A8" s="118" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="139" t="s">
+      <c r="B8" s="118" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="139" t="s">
+      <c r="C8" s="118" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="138" t="s">
+      <c r="A9" s="117" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="139" t="s">
+      <c r="B9" s="118" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="139" t="s">
+      <c r="C9" s="118" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="139" t="s">
+      <c r="A10" s="118" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="139" t="s">
+      <c r="B10" s="118" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="139" t="s">
+      <c r="C10" s="118" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="139" t="s">
+      <c r="A11" s="118" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="139" t="s">
+      <c r="B11" s="118" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="141" t="s">
+      <c r="C11" s="137" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="139" t="s">
+      <c r="A12" s="118" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="139" t="s">
+      <c r="B12" s="118" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="139" t="s">
+      <c r="C12" s="118" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="12" customHeight="1">
-      <c r="A13" s="139" t="s">
+      <c r="A13" s="118" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="139" t="s">
+      <c r="B13" s="118" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="142" t="s">
+      <c r="C13" s="120" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="139" t="s">
+      <c r="A14" s="118" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="139" t="s">
+      <c r="B14" s="118" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="139" t="s">
+      <c r="C14" s="118" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="139" t="s">
+      <c r="A15" s="118" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="139" t="s">
+      <c r="B15" s="118" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="139" t="s">
+      <c r="C15" s="118" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="138" t="s">
+      <c r="A16" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="139" t="s">
+      <c r="B16" s="118" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="139" t="s">
+      <c r="C16" s="118" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="138"/>
+      <c r="A17" s="117"/>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="138"/>
+      <c r="A18" s="117"/>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="138"/>
+      <c r="A19" s="117"/>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="138"/>
+      <c r="A20" s="117"/>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="138"/>
+      <c r="A21" s="117"/>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="138"/>
+      <c r="A22" s="117"/>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="138"/>
+      <c r="A23" s="117"/>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="138"/>
+      <c r="A24" s="117"/>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="138"/>
+      <c r="A25" s="117"/>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="138"/>
+      <c r="A26" s="117"/>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="138"/>
+      <c r="A27" s="117"/>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="138"/>
+      <c r="A28" s="117"/>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="138"/>
+      <c r="A29" s="117"/>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="138"/>
+      <c r="A30" s="117"/>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="138"/>
+      <c r="A31" s="117"/>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="138"/>
+      <c r="A32" s="117"/>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="138"/>
+      <c r="A33" s="117"/>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="138"/>
+      <c r="A34" s="117"/>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="138"/>
+      <c r="A35" s="117"/>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="138"/>
+      <c r="A36" s="117"/>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="138"/>
+      <c r="A37" s="117"/>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="138"/>
+      <c r="A38" s="117"/>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="138"/>
+      <c r="A39" s="117"/>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="138"/>
+      <c r="A40" s="117"/>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="138"/>
+      <c r="A41" s="117"/>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="138"/>
+      <c r="A42" s="117"/>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="138"/>
+      <c r="A43" s="117"/>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" s="138"/>
+      <c r="A44" s="117"/>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="138"/>
+      <c r="A45" s="117"/>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" s="138"/>
+      <c r="A46" s="117"/>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="138"/>
+      <c r="A47" s="117"/>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" s="138"/>
+      <c r="A48" s="117"/>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="138"/>
+      <c r="A49" s="117"/>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="138"/>
+      <c r="A50" s="117"/>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="138"/>
+      <c r="A51" s="117"/>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="138"/>
+      <c r="A52" s="117"/>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" s="138"/>
+      <c r="A53" s="117"/>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" s="138"/>
+      <c r="A54" s="117"/>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="138"/>
+      <c r="A55" s="117"/>
     </row>
     <row r="56" spans="1:1">
-      <c r="A56" s="138"/>
+      <c r="A56" s="117"/>
     </row>
     <row r="57" spans="1:1">
-      <c r="A57" s="138"/>
+      <c r="A57" s="117"/>
     </row>
     <row r="58" spans="1:1">
-      <c r="A58" s="138"/>
+      <c r="A58" s="117"/>
     </row>
     <row r="59" spans="1:1">
-      <c r="A59" s="138"/>
+      <c r="A59" s="117"/>
     </row>
     <row r="60" spans="1:1">
-      <c r="A60" s="138"/>
+      <c r="A60" s="117"/>
     </row>
     <row r="61" spans="1:1">
-      <c r="A61" s="138"/>
+      <c r="A61" s="117"/>
     </row>
     <row r="62" spans="1:1">
-      <c r="A62" s="138"/>
+      <c r="A62" s="117"/>
     </row>
     <row r="63" spans="1:1">
-      <c r="A63" s="138"/>
+      <c r="A63" s="117"/>
     </row>
     <row r="64" spans="1:1">
-      <c r="A64" s="138"/>
+      <c r="A64" s="117"/>
     </row>
     <row r="65" spans="1:1">
-      <c r="A65" s="138"/>
+      <c r="A65" s="117"/>
     </row>
     <row r="66" spans="1:1">
-      <c r="A66" s="138"/>
+      <c r="A66" s="117"/>
     </row>
     <row r="67" spans="1:1">
-      <c r="A67" s="138"/>
+      <c r="A67" s="117"/>
     </row>
     <row r="68" spans="1:1">
-      <c r="A68" s="138"/>
+      <c r="A68" s="117"/>
     </row>
     <row r="69" spans="1:1">
-      <c r="A69" s="138"/>
+      <c r="A69" s="117"/>
     </row>
     <row r="70" spans="1:1">
-      <c r="A70" s="138"/>
+      <c r="A70" s="117"/>
     </row>
     <row r="71" spans="1:1">
-      <c r="A71" s="138"/>
+      <c r="A71" s="117"/>
     </row>
     <row r="72" spans="1:1">
-      <c r="A72" s="138"/>
+      <c r="A72" s="117"/>
     </row>
     <row r="73" spans="1:1">
-      <c r="A73" s="138"/>
+      <c r="A73" s="117"/>
     </row>
     <row r="74" spans="1:1">
-      <c r="A74" s="138"/>
+      <c r="A74" s="117"/>
     </row>
     <row r="75" spans="1:1">
-      <c r="A75" s="138"/>
+      <c r="A75" s="117"/>
     </row>
     <row r="76" spans="1:1">
-      <c r="A76" s="138"/>
+      <c r="A76" s="117"/>
     </row>
     <row r="77" spans="1:1">
-      <c r="A77" s="138"/>
+      <c r="A77" s="117"/>
     </row>
     <row r="78" spans="1:1">
-      <c r="A78" s="138"/>
+      <c r="A78" s="117"/>
     </row>
     <row r="79" spans="1:1">
-      <c r="A79" s="138"/>
+      <c r="A79" s="117"/>
     </row>
     <row r="80" spans="1:1">
-      <c r="A80" s="138"/>
+      <c r="A80" s="117"/>
     </row>
     <row r="81" spans="1:1">
-      <c r="A81" s="138"/>
+      <c r="A81" s="117"/>
     </row>
     <row r="82" spans="1:1">
-      <c r="A82" s="138"/>
+      <c r="A82" s="117"/>
     </row>
     <row r="83" spans="1:1">
-      <c r="A83" s="138"/>
+      <c r="A83" s="117"/>
     </row>
     <row r="84" spans="1:1">
-      <c r="A84" s="138"/>
+      <c r="A84" s="117"/>
     </row>
     <row r="85" spans="1:1">
-      <c r="A85" s="138"/>
+      <c r="A85" s="117"/>
     </row>
     <row r="86" spans="1:1">
-      <c r="A86" s="138"/>
+      <c r="A86" s="117"/>
     </row>
     <row r="87" spans="1:1">
-      <c r="A87" s="138"/>
+      <c r="A87" s="117"/>
     </row>
     <row r="88" spans="1:1">
-      <c r="A88" s="138"/>
+      <c r="A88" s="117"/>
     </row>
     <row r="89" spans="1:1">
-      <c r="A89" s="138"/>
+      <c r="A89" s="117"/>
     </row>
     <row r="90" spans="1:1">
-      <c r="A90" s="138"/>
+      <c r="A90" s="117"/>
     </row>
     <row r="91" spans="1:1">
-      <c r="A91" s="138"/>
+      <c r="A91" s="117"/>
     </row>
     <row r="92" spans="1:1">
-      <c r="A92" s="138"/>
+      <c r="A92" s="117"/>
     </row>
     <row r="93" spans="1:1">
-      <c r="A93" s="138"/>
+      <c r="A93" s="117"/>
     </row>
     <row r="94" spans="1:1">
-      <c r="A94" s="138"/>
+      <c r="A94" s="117"/>
     </row>
     <row r="95" spans="1:1">
-      <c r="A95" s="138"/>
+      <c r="A95" s="117"/>
     </row>
     <row r="96" spans="1:1">
-      <c r="A96" s="138"/>
+      <c r="A96" s="117"/>
     </row>
     <row r="97" spans="1:1">
-      <c r="A97" s="138"/>
+      <c r="A97" s="117"/>
     </row>
     <row r="98" spans="1:1">
-      <c r="A98" s="138"/>
+      <c r="A98" s="117"/>
     </row>
     <row r="99" spans="1:1">
-      <c r="A99" s="138"/>
+      <c r="A99" s="117"/>
     </row>
     <row r="100" spans="1:1">
-      <c r="A100" s="138"/>
+      <c r="A100" s="117"/>
     </row>
     <row r="101" spans="1:1">
-      <c r="A101" s="138"/>
+      <c r="A101" s="117"/>
     </row>
     <row r="102" spans="1:1">
-      <c r="A102" s="138"/>
+      <c r="A102" s="117"/>
     </row>
     <row r="103" spans="1:1">
-      <c r="A103" s="138"/>
+      <c r="A103" s="117"/>
     </row>
     <row r="104" spans="1:1">
-      <c r="A104" s="138"/>
+      <c r="A104" s="117"/>
     </row>
     <row r="105" spans="1:1">
-      <c r="A105" s="138"/>
+      <c r="A105" s="117"/>
     </row>
     <row r="106" spans="1:1">
-      <c r="A106" s="138"/>
+      <c r="A106" s="117"/>
     </row>
     <row r="107" spans="1:1">
-      <c r="A107" s="138"/>
+      <c r="A107" s="117"/>
     </row>
     <row r="108" spans="1:1">
-      <c r="A108" s="138"/>
+      <c r="A108" s="117"/>
     </row>
     <row r="109" spans="1:1">
-      <c r="A109" s="138"/>
+      <c r="A109" s="117"/>
     </row>
     <row r="110" spans="1:1">
-      <c r="A110" s="138"/>
+      <c r="A110" s="117"/>
     </row>
     <row r="111" spans="1:1">
-      <c r="A111" s="138"/>
+      <c r="A111" s="117"/>
     </row>
     <row r="112" spans="1:1">
-      <c r="A112" s="138"/>
+      <c r="A112" s="117"/>
     </row>
     <row r="113" spans="1:1">
-      <c r="A113" s="138"/>
+      <c r="A113" s="117"/>
     </row>
     <row r="114" spans="1:1">
-      <c r="A114" s="138"/>
+      <c r="A114" s="117"/>
     </row>
     <row r="115" spans="1:1">
-      <c r="A115" s="138"/>
+      <c r="A115" s="117"/>
     </row>
     <row r="116" spans="1:1">
-      <c r="A116" s="138"/>
+      <c r="A116" s="117"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5225,194 +5030,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F46C07F1-1AE0-4A64-A0EA-5661CE7D091E}">
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
-  <cols>
-    <col min="1" max="1" width="21.140625" customWidth="1"/>
-    <col min="2" max="2" width="34.5703125" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="54" customWidth="1"/>
-    <col min="5" max="5" width="60.140625" customWidth="1"/>
-    <col min="6" max="7" width="8.85546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="35.450000000000003" customHeight="1">
-      <c r="A1" s="117" t="s">
-        <v>47</v>
-      </c>
-      <c r="B1" s="118"/>
-      <c r="C1" s="118"/>
-      <c r="D1" s="118"/>
-      <c r="E1" s="118"/>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="113" t="s">
-        <v>48</v>
-      </c>
-      <c r="B2" s="115" t="s">
-        <v>49</v>
-      </c>
-      <c r="C2" s="115" t="s">
-        <v>50</v>
-      </c>
-      <c r="D2" s="113" t="s">
-        <v>51</v>
-      </c>
-      <c r="E2" s="113" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="67.349999999999994" customHeight="1">
-      <c r="A3" s="78">
-        <v>1</v>
-      </c>
-      <c r="B3" s="54" t="s">
-        <v>53</v>
-      </c>
-      <c r="C3" s="54" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" s="79" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" s="55" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="64.7" customHeight="1">
-      <c r="A4" s="80">
-        <v>2</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4" s="81" t="s">
-        <v>58</v>
-      </c>
-      <c r="E4" s="58" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="15" customHeight="1">
-      <c r="A5" s="82"/>
-      <c r="B5" s="56"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="83"/>
-      <c r="E5" s="57"/>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="73" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="15" customHeight="1" thickBot="1">
-      <c r="A7" s="117" t="s">
-        <v>61</v>
-      </c>
-      <c r="B7" s="118"/>
-      <c r="C7" s="118"/>
-      <c r="D7" s="118"/>
-      <c r="E7" s="118"/>
-    </row>
-    <row r="8" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A8" s="113" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="115" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" s="115" t="s">
-        <v>63</v>
-      </c>
-      <c r="D8" s="115" t="s">
-        <v>64</v>
-      </c>
-      <c r="E8" s="113" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="84" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="85" t="s">
-        <v>66</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D9" s="86" t="s">
-        <v>68</v>
-      </c>
-      <c r="E9" s="84" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="84" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="85" t="s">
-        <v>70</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D10" s="86" t="s">
-        <v>68</v>
-      </c>
-      <c r="E10" s="84" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="84" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="85" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="D11" s="86" t="s">
-        <v>68</v>
-      </c>
-      <c r="E11" s="84" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="84" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="85" t="s">
-        <v>75</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E12" s="84" t="s">
-        <v>77</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A7:E7"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCD42993-36AA-467C-AC72-C7D2E881EEDA}">
   <dimension ref="A1:E31"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
@@ -5425,13 +5042,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="36.75" customHeight="1">
-      <c r="A1" s="121" t="s">
-        <v>78</v>
-      </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
+      <c r="A1" s="151" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="152"/>
+      <c r="C1" s="152"/>
+      <c r="D1" s="152"/>
+      <c r="E1" s="152"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="7" t="s">
@@ -5458,13 +5075,13 @@
         <v>19</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="D3" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" s="12" t="s">
         <v>55</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="11" customFormat="1" ht="231.95">
@@ -5472,13 +5089,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="E4" s="12"/>
     </row>
@@ -5487,13 +5104,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="E5" s="12"/>
     </row>
@@ -5502,13 +5119,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="E6" s="12"/>
     </row>
@@ -5517,16 +5134,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="57.95">
@@ -5534,16 +5151,16 @@
         <v>6</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="144.94999999999999">
@@ -5551,16 +5168,16 @@
         <v>7</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="11" customFormat="1">
@@ -5571,29 +5188,29 @@
       <c r="E10"/>
     </row>
     <row r="11" spans="1:5" s="11" customFormat="1" ht="14.45" customHeight="1" thickBot="1">
-      <c r="A11" s="119" t="s">
-        <v>95</v>
-      </c>
-      <c r="B11" s="120"/>
-      <c r="C11" s="120"/>
-      <c r="D11" s="120"/>
-      <c r="E11" s="120"/>
+      <c r="A11" s="149" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="150"/>
+      <c r="C11" s="150"/>
+      <c r="D11" s="150"/>
+      <c r="E11" s="150"/>
     </row>
     <row r="12" spans="1:5" s="11" customFormat="1" ht="29.1">
       <c r="A12" s="104" t="s">
         <v>29</v>
       </c>
       <c r="B12" s="105" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="C12" s="105" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="D12" s="104" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="E12" s="104" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:5" s="11" customFormat="1">
@@ -5601,13 +5218,13 @@
         <v>7</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>19</v>
@@ -5618,16 +5235,16 @@
         <v>7</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -5635,13 +5252,13 @@
         <v>7</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>19</v>
@@ -5652,13 +5269,13 @@
         <v>7</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>16</v>
@@ -5669,13 +5286,13 @@
         <v>7</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>19</v>
@@ -5686,13 +5303,13 @@
         <v>7</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>19</v>
@@ -5703,16 +5320,16 @@
         <v>7</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -5720,13 +5337,13 @@
         <v>7</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>19</v>
@@ -5737,13 +5354,13 @@
         <v>7</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>19</v>
@@ -5754,13 +5371,13 @@
         <v>7</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>19</v>
@@ -5771,13 +5388,13 @@
         <v>7</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>19</v>
@@ -5788,13 +5405,13 @@
         <v>7</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>19</v>
@@ -5805,13 +5422,13 @@
         <v>7</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>19</v>
@@ -5822,13 +5439,13 @@
         <v>7</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>19</v>
@@ -5839,13 +5456,13 @@
         <v>7</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>19</v>
@@ -5856,13 +5473,13 @@
         <v>7</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>19</v>
@@ -5873,13 +5490,13 @@
         <v>7</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>19</v>
@@ -5890,13 +5507,13 @@
         <v>7</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>19</v>
@@ -5913,241 +5530,1615 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A14F5E4-DCD2-4C2B-80EA-545272C1842A}">
-  <dimension ref="A1:E15"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CF1D022-2DCA-4C9F-85B3-06476B5333EE}">
+  <dimension ref="A1:F32"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="14.140625" customWidth="1"/>
-    <col min="2" max="2" width="52.5703125" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="105.5703125" customWidth="1"/>
-    <col min="5" max="5" width="42.42578125" customWidth="1"/>
-    <col min="6" max="7" width="8.85546875" customWidth="1"/>
+    <col min="1" max="1" width="18" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="72.5703125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" style="6" customWidth="1"/>
+    <col min="4" max="4" width="19.7109375" style="6" customWidth="1"/>
+    <col min="5" max="5" width="55.5703125" style="6" customWidth="1"/>
+    <col min="6" max="6" width="25" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="25.7" customHeight="1">
-      <c r="A1" s="117" t="s">
+    <row r="1" spans="1:6" ht="31.5" customHeight="1">
+      <c r="A1" s="153" t="s">
+        <v>118</v>
+      </c>
+      <c r="B1" s="154"/>
+      <c r="C1" s="154"/>
+      <c r="D1" s="154"/>
+      <c r="E1" s="155"/>
+      <c r="F1"/>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="99" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" s="98" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="98" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="100" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="98" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2"/>
+    </row>
+    <row r="3" spans="1:6" ht="264.75" customHeight="1">
+      <c r="A3" s="18">
+        <v>1</v>
+      </c>
+      <c r="B3" s="95" t="s">
+        <v>119</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" s="96" t="s">
+        <v>121</v>
+      </c>
+      <c r="F3"/>
+    </row>
+    <row r="4" spans="1:6" ht="240" customHeight="1">
+      <c r="A4" s="20">
+        <v>2</v>
+      </c>
+      <c r="B4" s="95" t="s">
+        <v>122</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="E4" s="96" t="s">
+        <v>124</v>
+      </c>
+      <c r="F4"/>
+    </row>
+    <row r="5" spans="1:6" ht="159.6">
+      <c r="A5" s="20">
+        <v>3</v>
+      </c>
+      <c r="B5" s="95" t="s">
+        <v>125</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" s="96" t="s">
+        <v>127</v>
+      </c>
+      <c r="F5"/>
+    </row>
+    <row r="6" spans="1:6" ht="186" customHeight="1">
+      <c r="A6" s="19">
+        <v>4</v>
+      </c>
+      <c r="B6" s="95" t="s">
+        <v>128</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="96" t="s">
+        <v>130</v>
+      </c>
+      <c r="F6"/>
+    </row>
+    <row r="7" spans="1:6" ht="195.75" customHeight="1">
+      <c r="A7" s="19">
+        <v>5</v>
+      </c>
+      <c r="B7" s="95" t="s">
+        <v>131</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7" s="96" t="s">
+        <v>133</v>
+      </c>
+      <c r="F7"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="51" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="156" t="s">
+        <v>135</v>
+      </c>
+      <c r="B10" s="156"/>
+      <c r="C10" s="156"/>
+      <c r="D10" s="156"/>
+      <c r="E10" s="156"/>
+      <c r="F10" s="156"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="101" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="102" t="s">
+        <v>136</v>
+      </c>
+      <c r="C11" s="102" t="s">
+        <v>137</v>
+      </c>
+      <c r="D11" s="103" t="s">
         <v>138</v>
       </c>
-      <c r="B1" s="118"/>
-      <c r="C1" s="118"/>
-      <c r="D1" s="118"/>
-      <c r="E1" s="118"/>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="113" t="s">
-        <v>48</v>
-      </c>
-      <c r="B2" s="113" t="s">
-        <v>49</v>
-      </c>
-      <c r="C2" s="113" t="s">
-        <v>50</v>
-      </c>
-      <c r="D2" s="113" t="s">
-        <v>51</v>
-      </c>
-      <c r="E2" s="113" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="290.10000000000002">
-      <c r="A3" s="3">
-        <v>1</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="E11" s="102" t="s">
+        <v>76</v>
+      </c>
+      <c r="F11" s="102" t="s">
         <v>139</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" s="3"/>
-    </row>
-    <row r="4" spans="1:5" ht="288.75" customHeight="1">
-      <c r="A4" s="2">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="s">
+    </row>
+    <row r="12" spans="1:6" ht="17.25" customHeight="1">
+      <c r="A12" s="94" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="94" t="s">
         <v>140</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C12" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D12" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="E12" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F12" s="93" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="18.75" customHeight="1">
-      <c r="A5" s="53"/>
-      <c r="B5" s="53"/>
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="73" t="s">
+    <row r="13" spans="1:6">
+      <c r="A13" s="94" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="94" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" s="19" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="34.5" customHeight="1">
-      <c r="A7" s="123" t="s">
+      <c r="D13" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="E13" s="22" t="s">
         <v>145</v>
       </c>
-      <c r="B7" s="124"/>
-      <c r="C7" s="124"/>
-      <c r="D7" s="124"/>
-      <c r="E7" s="124"/>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="114" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="113" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" s="115" t="s">
-        <v>63</v>
-      </c>
-      <c r="D8" s="113" t="s">
-        <v>64</v>
-      </c>
-      <c r="E8" s="116" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="87" t="s">
+      <c r="F13" s="93" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="94" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="94" t="s">
         <v>146</v>
       </c>
-      <c r="B9" s="85" t="s">
-        <v>72</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="D9" s="86" t="s">
-        <v>68</v>
-      </c>
-      <c r="E9" s="88" t="s">
+      <c r="C14" s="97" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" ht="101.45">
-      <c r="A10" s="87" t="s">
-        <v>146</v>
-      </c>
-      <c r="B10" s="85" t="s">
+      <c r="D14" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="E14" s="22" t="s">
         <v>148</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="F14" s="93" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="94" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="94" t="s">
+        <v>84</v>
+      </c>
+      <c r="C15" s="97" t="s">
+        <v>147</v>
+      </c>
+      <c r="D15" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="E15" s="22" t="s">
         <v>149</v>
       </c>
-      <c r="D10" s="86" t="s">
-        <v>68</v>
-      </c>
-      <c r="E10" s="88" t="s">
+      <c r="F15" s="93" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="29.1">
-      <c r="A11" s="87" t="s">
-        <v>146</v>
-      </c>
-      <c r="B11" s="85" t="s">
+    <row r="16" spans="1:6">
+      <c r="A16" s="94" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="94" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" s="97" t="s">
+        <v>147</v>
+      </c>
+      <c r="D16" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E16" s="22" t="s">
         <v>151</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="F16" s="93" t="s">
         <v>152</v>
       </c>
-      <c r="D11" s="86" t="s">
-        <v>68</v>
-      </c>
-      <c r="E11" s="88" t="s">
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="94" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="94" t="s">
+        <v>90</v>
+      </c>
+      <c r="C17" s="97" t="s">
+        <v>147</v>
+      </c>
+      <c r="D17" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E17" s="26" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="87" t="s">
-        <v>146</v>
-      </c>
-      <c r="B12" s="85" t="s">
+      <c r="F17" s="93" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="94" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="94" t="s">
+        <v>112</v>
+      </c>
+      <c r="C18" s="97" t="s">
+        <v>147</v>
+      </c>
+      <c r="D18" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E18" s="26" t="s">
         <v>154</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="F18" s="93" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="94" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="94" t="s">
+        <v>92</v>
+      </c>
+      <c r="C19" s="97" t="s">
+        <v>147</v>
+      </c>
+      <c r="D19" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E19" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="F19" s="93" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="94" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="94" t="s">
+        <v>96</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>157</v>
+      </c>
+      <c r="D20" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="F20" s="93" t="s">
         <v>152</v>
       </c>
-      <c r="D12" s="86" t="s">
-        <v>68</v>
-      </c>
-      <c r="E12" s="88" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="87" t="s">
-        <v>146</v>
-      </c>
-      <c r="B13" s="85" t="s">
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="94" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="94" t="s">
+        <v>98</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>157</v>
+      </c>
+      <c r="D21" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E21" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="F21" s="93" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="94" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="94" t="s">
+        <v>160</v>
+      </c>
+      <c r="C22" s="97" t="s">
+        <v>147</v>
+      </c>
+      <c r="D22" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E22" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="F22" s="93" t="s">
         <v>156</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D13" s="86" t="s">
-        <v>68</v>
-      </c>
-      <c r="E13" s="88" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="43.5">
-      <c r="A14" s="87" t="s">
-        <v>146</v>
-      </c>
-      <c r="B14" s="85" t="s">
-        <v>158</v>
-      </c>
-      <c r="C14" s="5" t="s">
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="94" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="94" t="s">
+        <v>114</v>
+      </c>
+      <c r="C23" s="97" t="s">
+        <v>147</v>
+      </c>
+      <c r="D23" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E23" s="26" t="s">
+        <v>162</v>
+      </c>
+      <c r="F23" s="93" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="94" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" s="94" t="s">
+        <v>100</v>
+      </c>
+      <c r="C24" s="97" t="s">
+        <v>147</v>
+      </c>
+      <c r="D24" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E24" s="26" t="s">
+        <v>163</v>
+      </c>
+      <c r="F24" s="93" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="94" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25" s="94" t="s">
+        <v>102</v>
+      </c>
+      <c r="C25" s="97" t="s">
+        <v>147</v>
+      </c>
+      <c r="D25" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E25" s="26" t="s">
+        <v>164</v>
+      </c>
+      <c r="F25" s="93" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="94" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26" s="94" t="s">
+        <v>104</v>
+      </c>
+      <c r="C26" s="97" t="s">
+        <v>147</v>
+      </c>
+      <c r="D26" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="E26" s="26" t="s">
+        <v>165</v>
+      </c>
+      <c r="F26" s="93" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="94" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" s="94" t="s">
+        <v>116</v>
+      </c>
+      <c r="C27" s="97" t="s">
+        <v>147</v>
+      </c>
+      <c r="D27" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E27" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="F27" s="93" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="94" t="s">
+        <v>19</v>
+      </c>
+      <c r="B28" s="94" t="s">
+        <v>167</v>
+      </c>
+      <c r="C28" s="97" t="s">
+        <v>147</v>
+      </c>
+      <c r="D28" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E28" s="26" t="s">
+        <v>168</v>
+      </c>
+      <c r="F28" s="93" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="94" t="s">
+        <v>19</v>
+      </c>
+      <c r="B29" s="94" t="s">
+        <v>106</v>
+      </c>
+      <c r="C29" s="97" t="s">
+        <v>147</v>
+      </c>
+      <c r="D29" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E29" s="26" t="s">
+        <v>169</v>
+      </c>
+      <c r="F29" s="93" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="94" t="s">
+        <v>19</v>
+      </c>
+      <c r="B30" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="C30" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="D30" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E30" s="22" t="s">
+        <v>171</v>
+      </c>
+      <c r="F30" s="93" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="94" t="s">
+        <v>19</v>
+      </c>
+      <c r="B31" s="94" t="s">
+        <v>110</v>
+      </c>
+      <c r="C31" s="24" t="s">
+        <v>173</v>
+      </c>
+      <c r="D31" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E31" s="22" t="s">
+        <v>174</v>
+      </c>
+      <c r="F31" s="93" t="s">
         <v>152</v>
       </c>
-      <c r="D14" s="86" t="s">
-        <v>68</v>
-      </c>
-      <c r="E14" s="88" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="37.5" customHeight="1">
-      <c r="A15" s="89" t="s">
-        <v>146</v>
-      </c>
-      <c r="B15" s="90" t="s">
-        <v>160</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D15" s="91" t="s">
-        <v>68</v>
-      </c>
-      <c r="E15" s="92" t="s">
-        <v>161</v>
-      </c>
-    </row>
+    </row>
+    <row r="32" spans="1:6" ht="15"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A10:F10"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37797131-4575-41AC-AB4A-64D0D662358B}">
+  <dimension ref="A1:F54"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
+  <cols>
+    <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="63.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="68.5703125" customWidth="1"/>
+    <col min="6" max="6" width="32.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="157" t="s">
+        <v>175</v>
+      </c>
+      <c r="B1" s="158"/>
+      <c r="C1" s="158"/>
+      <c r="D1" s="158"/>
+      <c r="E1" s="159"/>
+      <c r="F1" s="17"/>
+    </row>
+    <row r="2" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A2" s="107" t="s">
+        <v>176</v>
+      </c>
+      <c r="B2" s="107"/>
+      <c r="C2" s="107"/>
+      <c r="D2" s="107"/>
+      <c r="E2" s="107"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="108" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="106" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="106" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="109" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" s="106" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="29.1">
+      <c r="A4" s="9">
+        <v>1</v>
+      </c>
+      <c r="B4" s="27" t="s">
+        <v>178</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>179</v>
+      </c>
+      <c r="D4" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="E4" s="27" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="181.5" customHeight="1">
+      <c r="A5" s="9">
+        <v>2</v>
+      </c>
+      <c r="B5" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>120</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" s="27" t="s">
+        <v>182</v>
+      </c>
+      <c r="F5" s="17"/>
+    </row>
+    <row r="6" spans="1:6" ht="153" customHeight="1">
+      <c r="A6" s="9">
+        <v>3</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>183</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>184</v>
+      </c>
+      <c r="D6" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="27" t="s">
+        <v>185</v>
+      </c>
+      <c r="F6" s="17"/>
+    </row>
+    <row r="7" spans="1:6" ht="215.25" customHeight="1">
+      <c r="A7" s="9">
+        <v>4</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>186</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>129</v>
+      </c>
+      <c r="D7" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>187</v>
+      </c>
+      <c r="F7" s="17"/>
+    </row>
+    <row r="8" spans="1:6" ht="174" customHeight="1">
+      <c r="A8" s="9">
+        <v>5</v>
+      </c>
+      <c r="B8" s="27" t="s">
+        <v>188</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>189</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="E8" s="27" t="s">
+        <v>190</v>
+      </c>
+      <c r="F8" s="17"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="17"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="51" t="s">
+        <v>134</v>
+      </c>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="156" t="s">
+        <v>191</v>
+      </c>
+      <c r="B11" s="156"/>
+      <c r="C11" s="156"/>
+      <c r="D11" s="156"/>
+      <c r="E11" s="156"/>
+      <c r="F11" s="156"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="101" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="102" t="s">
+        <v>136</v>
+      </c>
+      <c r="C12" s="102" t="s">
+        <v>137</v>
+      </c>
+      <c r="D12" s="103" t="s">
+        <v>138</v>
+      </c>
+      <c r="E12" s="102" t="s">
+        <v>76</v>
+      </c>
+      <c r="F12" s="102" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="D13" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E13" s="27" t="s">
+        <v>194</v>
+      </c>
+      <c r="F13" s="28" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="28" t="s">
+        <v>195</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>196</v>
+      </c>
+      <c r="D14" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E14" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="F14" s="28" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="C15" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="E15" s="28" t="s">
+        <v>198</v>
+      </c>
+      <c r="F15" s="28" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="C16" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D16" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="E16" s="28" t="s">
+        <v>200</v>
+      </c>
+      <c r="F16" s="28" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" s="28" t="s">
+        <v>202</v>
+      </c>
+      <c r="C17" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D17" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="E17" s="28" t="s">
+        <v>203</v>
+      </c>
+      <c r="F17" s="28" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="C18" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="E18" s="28" t="s">
+        <v>205</v>
+      </c>
+      <c r="F18" s="28" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" s="28" t="s">
+        <v>206</v>
+      </c>
+      <c r="C19" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D19" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="E19" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="F19" s="28" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="28" t="s">
+        <v>208</v>
+      </c>
+      <c r="C20" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D20" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="E20" s="28" t="s">
+        <v>209</v>
+      </c>
+      <c r="F20" s="28" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="C21" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D21" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="E21" s="28" t="s">
+        <v>211</v>
+      </c>
+      <c r="F21" s="28" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" s="28" t="s">
+        <v>212</v>
+      </c>
+      <c r="C22" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D22" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="E22" s="28" t="s">
+        <v>213</v>
+      </c>
+      <c r="F22" s="28" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="C23" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="D23" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="E23" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="F23" s="30" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24" s="28" t="s">
+        <v>217</v>
+      </c>
+      <c r="C24" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="E24" s="28" t="s">
+        <v>218</v>
+      </c>
+      <c r="F24" s="28" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" s="28" t="s">
+        <v>219</v>
+      </c>
+      <c r="C25" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="E25" s="28" t="s">
+        <v>220</v>
+      </c>
+      <c r="F25" s="28" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="B26" s="32" t="s">
+        <v>221</v>
+      </c>
+      <c r="C26" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D26" s="33" t="s">
+        <v>79</v>
+      </c>
+      <c r="E26" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="F26" s="32" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B27" s="28" t="s">
+        <v>223</v>
+      </c>
+      <c r="C27" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D27" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E27" s="28" t="s">
+        <v>224</v>
+      </c>
+      <c r="F27" s="28" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" s="28" t="s">
+        <v>225</v>
+      </c>
+      <c r="C28" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D28" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E28" s="28" t="s">
+        <v>226</v>
+      </c>
+      <c r="F28" s="28" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" s="28" t="s">
+        <v>228</v>
+      </c>
+      <c r="C29" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D29" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E29" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="F29" s="28" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B30" s="28" t="s">
+        <v>230</v>
+      </c>
+      <c r="C30" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D30" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E30" s="28" t="s">
+        <v>231</v>
+      </c>
+      <c r="F30" s="28" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" s="28" t="s">
+        <v>232</v>
+      </c>
+      <c r="C31" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D31" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E31" s="28" t="s">
+        <v>233</v>
+      </c>
+      <c r="F31" s="28" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32" s="28" t="s">
+        <v>234</v>
+      </c>
+      <c r="C32" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D32" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E32" s="28" t="s">
+        <v>235</v>
+      </c>
+      <c r="F32" s="28" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B33" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="C33" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D33" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E33" s="28" t="s">
+        <v>237</v>
+      </c>
+      <c r="F33" s="28" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B34" s="28" t="s">
+        <v>238</v>
+      </c>
+      <c r="C34" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D34" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E34" s="28" t="s">
+        <v>239</v>
+      </c>
+      <c r="F34" s="28" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35" s="28" t="s">
+        <v>240</v>
+      </c>
+      <c r="C35" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D35" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E35" s="28" t="s">
+        <v>241</v>
+      </c>
+      <c r="F35" s="28" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B36" s="28" t="s">
+        <v>242</v>
+      </c>
+      <c r="C36" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D36" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E36" s="28" t="s">
+        <v>243</v>
+      </c>
+      <c r="F36" s="28" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37" s="28" t="s">
+        <v>244</v>
+      </c>
+      <c r="C37" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D37" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E37" s="28" t="s">
+        <v>245</v>
+      </c>
+      <c r="F37" s="28" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B38" s="28" t="s">
+        <v>246</v>
+      </c>
+      <c r="C38" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D38" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E38" s="28" t="s">
+        <v>247</v>
+      </c>
+      <c r="F38" s="28" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B39" s="28" t="s">
+        <v>248</v>
+      </c>
+      <c r="C39" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D39" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E39" s="28" t="s">
+        <v>249</v>
+      </c>
+      <c r="F39" s="28" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B40" s="28" t="s">
+        <v>250</v>
+      </c>
+      <c r="C40" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="D40" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E40" s="28" t="s">
+        <v>252</v>
+      </c>
+      <c r="F40" s="28" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B41" s="28" t="s">
+        <v>254</v>
+      </c>
+      <c r="C41" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="D41" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E41" s="28" t="s">
+        <v>255</v>
+      </c>
+      <c r="F41" s="28" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B42" s="28" t="s">
+        <v>256</v>
+      </c>
+      <c r="C42" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D42" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E42" s="28" t="s">
+        <v>257</v>
+      </c>
+      <c r="F42" s="28" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B43" s="28" t="s">
+        <v>258</v>
+      </c>
+      <c r="C43" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D43" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E43" s="28" t="s">
+        <v>259</v>
+      </c>
+      <c r="F43" s="28" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" s="28" t="s">
+        <v>261</v>
+      </c>
+      <c r="C44" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D44" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E44" s="28" t="s">
+        <v>262</v>
+      </c>
+      <c r="F44" s="28" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B45" s="28" t="s">
+        <v>263</v>
+      </c>
+      <c r="C45" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D45" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E45" s="28" t="s">
+        <v>264</v>
+      </c>
+      <c r="F45" s="28" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B46" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="C46" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D46" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="E46" s="28" t="s">
+        <v>266</v>
+      </c>
+      <c r="F46" s="28" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B47" s="28" t="s">
+        <v>268</v>
+      </c>
+      <c r="C47" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="D47" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E47" s="28" t="s">
+        <v>269</v>
+      </c>
+      <c r="F47" s="28" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B48" s="28" t="s">
+        <v>270</v>
+      </c>
+      <c r="C48" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D48" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E48" s="28" t="s">
+        <v>271</v>
+      </c>
+      <c r="F48" s="28" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B49" s="28" t="s">
+        <v>272</v>
+      </c>
+      <c r="C49" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D49" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E49" s="28" t="s">
+        <v>273</v>
+      </c>
+      <c r="F49" s="28" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B50" s="28" t="s">
+        <v>274</v>
+      </c>
+      <c r="C50" s="28" t="s">
+        <v>275</v>
+      </c>
+      <c r="D50" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E50" s="28" t="s">
+        <v>276</v>
+      </c>
+      <c r="F50" s="28" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B51" s="28" t="s">
+        <v>278</v>
+      </c>
+      <c r="C51" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D51" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E51" s="28" t="s">
+        <v>279</v>
+      </c>
+      <c r="F51" s="28" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B52" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="C52" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D52" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E52" s="28" t="s">
+        <v>281</v>
+      </c>
+      <c r="F52" s="28" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B53" s="28" t="s">
+        <v>282</v>
+      </c>
+      <c r="C53" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D53" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E53" s="27" t="s">
+        <v>283</v>
+      </c>
+      <c r="F53" s="28" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B54" s="28" t="s">
+        <v>284</v>
+      </c>
+      <c r="C54" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="D54" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E54" s="27" t="s">
+        <v>286</v>
+      </c>
+      <c r="F54" s="28" t="s">
+        <v>287</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A11:F11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
@@ -6165,19 +7156,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="34.5" customHeight="1">
-      <c r="A1" s="127" t="s">
-        <v>162</v>
-      </c>
-      <c r="B1" s="127"/>
-      <c r="C1" s="127"/>
-      <c r="D1" s="127"/>
-      <c r="E1" s="127"/>
-      <c r="F1" s="127"/>
+      <c r="A1" s="162" t="s">
+        <v>288</v>
+      </c>
+      <c r="B1" s="162"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="162"/>
       <c r="G1" s="42"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="111" t="s">
-        <v>163</v>
+        <v>289</v>
       </c>
       <c r="B2" s="111"/>
       <c r="C2" s="111"/>
@@ -6214,11 +7205,11 @@
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E4" s="49"/>
       <c r="F4" s="49" t="s">
-        <v>164</v>
+        <v>290</v>
       </c>
       <c r="G4" s="42"/>
     </row>
@@ -6235,20 +7226,20 @@
       <c r="A6" s="43"/>
       <c r="B6" s="44"/>
       <c r="C6" s="45"/>
-      <c r="D6" s="125"/>
-      <c r="E6" s="125"/>
+      <c r="D6" s="160"/>
+      <c r="E6" s="160"/>
       <c r="F6" s="46"/>
       <c r="G6" s="42"/>
     </row>
     <row r="7" spans="1:7" ht="13.5" customHeight="1">
-      <c r="A7" s="126" t="s">
-        <v>165</v>
-      </c>
-      <c r="B7" s="126"/>
-      <c r="C7" s="126"/>
-      <c r="D7" s="126"/>
-      <c r="E7" s="126"/>
-      <c r="F7" s="126"/>
+      <c r="A7" s="161" t="s">
+        <v>291</v>
+      </c>
+      <c r="B7" s="161"/>
+      <c r="C7" s="161"/>
+      <c r="D7" s="161"/>
+      <c r="E7" s="161"/>
+      <c r="F7" s="161"/>
       <c r="G7" s="42"/>
     </row>
     <row r="8" spans="1:7">
@@ -6256,19 +7247,19 @@
         <v>29</v>
       </c>
       <c r="B8" s="112" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="C8" s="112" t="s">
-        <v>63</v>
+        <v>137</v>
       </c>
       <c r="D8" s="112" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="E8" s="112" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="F8" s="112" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="G8" s="42"/>
     </row>
@@ -6277,16 +7268,16 @@
         <v>16</v>
       </c>
       <c r="B9" s="48" t="s">
-        <v>167</v>
+        <v>292</v>
       </c>
       <c r="C9" s="49" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D9" s="50" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E9" s="48" t="s">
-        <v>168</v>
+        <v>293</v>
       </c>
       <c r="F9" s="49" t="s">
         <v>17</v>
@@ -6298,16 +7289,16 @@
         <v>16</v>
       </c>
       <c r="B10" s="48" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="C10" s="49" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D10" s="50" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E10" s="48" t="s">
-        <v>169</v>
+        <v>294</v>
       </c>
       <c r="F10" s="49" t="s">
         <v>17</v>
@@ -6319,16 +7310,16 @@
         <v>16</v>
       </c>
       <c r="B11" s="48" t="s">
-        <v>170</v>
+        <v>295</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D11" s="50" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E11" s="48" t="s">
-        <v>171</v>
+        <v>296</v>
       </c>
       <c r="F11" s="49" t="s">
         <v>17</v>
@@ -6340,16 +7331,16 @@
         <v>16</v>
       </c>
       <c r="B12" s="48" t="s">
-        <v>172</v>
+        <v>297</v>
       </c>
       <c r="C12" s="49" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D12" s="50" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E12" s="48" t="s">
-        <v>173</v>
+        <v>298</v>
       </c>
       <c r="F12" s="49" t="s">
         <v>17</v>
@@ -6361,16 +7352,16 @@
         <v>16</v>
       </c>
       <c r="B13" s="48" t="s">
-        <v>174</v>
+        <v>299</v>
       </c>
       <c r="C13" s="49" t="s">
-        <v>73</v>
+        <v>193</v>
       </c>
       <c r="D13" s="50" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E13" s="48" t="s">
-        <v>174</v>
+        <v>299</v>
       </c>
       <c r="F13" s="49" t="s">
         <v>17</v>
@@ -6453,13 +7444,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="128" t="s">
-        <v>175</v>
-      </c>
-      <c r="B1" s="129"/>
-      <c r="C1" s="129"/>
-      <c r="D1" s="129"/>
-      <c r="E1" s="130"/>
+      <c r="A1" s="163" t="s">
+        <v>300</v>
+      </c>
+      <c r="B1" s="164"/>
+      <c r="C1" s="164"/>
+      <c r="D1" s="164"/>
+      <c r="E1" s="165"/>
       <c r="F1" s="74"/>
       <c r="G1" s="59"/>
     </row>
@@ -6487,16 +7478,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="64" t="s">
-        <v>176</v>
+        <v>301</v>
       </c>
       <c r="C3" s="64" t="s">
-        <v>177</v>
+        <v>120</v>
       </c>
       <c r="D3" s="64" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E3" s="64" t="s">
-        <v>178</v>
+        <v>302</v>
       </c>
       <c r="F3" s="74"/>
       <c r="G3" s="61"/>
@@ -6506,16 +7497,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="64" t="s">
-        <v>179</v>
+        <v>303</v>
       </c>
       <c r="C4" s="64" t="s">
-        <v>180</v>
+        <v>123</v>
       </c>
       <c r="D4" s="64" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="E4" s="64" t="s">
-        <v>181</v>
+        <v>304</v>
       </c>
       <c r="F4" s="74"/>
       <c r="G4" s="61"/>
@@ -6525,16 +7516,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="64" t="s">
-        <v>182</v>
+        <v>305</v>
       </c>
       <c r="C5" s="64" t="s">
-        <v>183</v>
+        <v>306</v>
       </c>
       <c r="D5" s="64" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="E5" s="64" t="s">
-        <v>184</v>
+        <v>307</v>
       </c>
       <c r="F5" s="74"/>
       <c r="G5" s="61"/>
@@ -6544,16 +7535,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="64" t="s">
-        <v>185</v>
+        <v>308</v>
       </c>
       <c r="C6" s="64" t="s">
-        <v>186</v>
+        <v>309</v>
       </c>
       <c r="D6" s="64" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="E6" s="64" t="s">
-        <v>187</v>
+        <v>310</v>
       </c>
       <c r="F6" s="74"/>
       <c r="G6" s="61"/>
@@ -6563,16 +7554,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="64" t="s">
-        <v>188</v>
+        <v>311</v>
       </c>
       <c r="C7" s="64" t="s">
-        <v>189</v>
+        <v>312</v>
       </c>
       <c r="D7" s="64" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="E7" s="64" t="s">
-        <v>190</v>
+        <v>313</v>
       </c>
       <c r="F7" s="74"/>
       <c r="G7" s="61"/>
@@ -6582,16 +7573,16 @@
         <v>6</v>
       </c>
       <c r="B8" s="64" t="s">
-        <v>191</v>
+        <v>314</v>
       </c>
       <c r="C8" s="64" t="s">
-        <v>192</v>
+        <v>315</v>
       </c>
       <c r="D8" s="64" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="E8" s="64" t="s">
-        <v>193</v>
+        <v>316</v>
       </c>
       <c r="F8" s="74"/>
       <c r="G8" s="61"/>
@@ -6601,11 +7592,11 @@
         <v>7</v>
       </c>
       <c r="B9" s="76" t="s">
-        <v>194</v>
+        <v>317</v>
       </c>
       <c r="C9" s="76"/>
       <c r="D9" s="76" t="s">
-        <v>195</v>
+        <v>318</v>
       </c>
       <c r="E9" s="76"/>
       <c r="F9" s="60"/>
@@ -6613,7 +7604,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="70" t="s">
-        <v>196</v>
+        <v>319</v>
       </c>
       <c r="B10" s="71"/>
       <c r="C10" s="71"/>
@@ -6624,22 +7615,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="110" t="s">
-        <v>197</v>
+        <v>320</v>
       </c>
       <c r="B11" s="110" t="s">
-        <v>198</v>
+        <v>321</v>
       </c>
       <c r="C11" s="110" t="s">
-        <v>199</v>
+        <v>322</v>
       </c>
       <c r="D11" s="110" t="s">
         <v>28</v>
       </c>
       <c r="E11" s="110" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="F11" s="75" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="G11" s="62"/>
     </row>
@@ -6648,16 +7639,16 @@
         <v>17</v>
       </c>
       <c r="B12" s="64" t="s">
-        <v>200</v>
+        <v>323</v>
       </c>
       <c r="C12" s="65" t="s">
-        <v>201</v>
+        <v>324</v>
       </c>
       <c r="D12" s="66" t="s">
-        <v>202</v>
+        <v>325</v>
       </c>
       <c r="E12" s="64" t="s">
-        <v>203</v>
+        <v>326</v>
       </c>
       <c r="F12" s="76"/>
       <c r="G12" s="60"/>
@@ -6667,19 +7658,19 @@
         <v>17</v>
       </c>
       <c r="B13" s="64" t="s">
-        <v>174</v>
+        <v>299</v>
       </c>
       <c r="C13" s="67" t="s">
-        <v>204</v>
+        <v>327</v>
       </c>
       <c r="D13" s="69" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E13" s="64" t="s">
-        <v>205</v>
+        <v>328</v>
       </c>
       <c r="F13" s="77" t="s">
-        <v>206</v>
+        <v>150</v>
       </c>
       <c r="G13" s="60"/>
     </row>
@@ -6688,19 +7679,19 @@
         <v>17</v>
       </c>
       <c r="B14" s="64" t="s">
-        <v>171</v>
+        <v>296</v>
       </c>
       <c r="C14" s="65" t="s">
-        <v>204</v>
+        <v>327</v>
       </c>
       <c r="D14" s="66" t="s">
-        <v>202</v>
+        <v>325</v>
       </c>
       <c r="E14" s="64" t="s">
-        <v>207</v>
+        <v>329</v>
       </c>
       <c r="F14" s="77" t="s">
-        <v>208</v>
+        <v>330</v>
       </c>
       <c r="G14" s="60"/>
     </row>
@@ -6709,19 +7700,19 @@
         <v>17</v>
       </c>
       <c r="B15" s="64" t="s">
-        <v>173</v>
+        <v>298</v>
       </c>
       <c r="C15" s="65" t="s">
-        <v>204</v>
+        <v>327</v>
       </c>
       <c r="D15" s="69" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E15" s="64" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="F15" s="77" t="s">
-        <v>206</v>
+        <v>150</v>
       </c>
       <c r="G15" s="60"/>
     </row>
@@ -6730,19 +7721,19 @@
         <v>17</v>
       </c>
       <c r="B16" s="68" t="s">
-        <v>210</v>
+        <v>331</v>
       </c>
       <c r="C16" s="68" t="s">
-        <v>204</v>
+        <v>327</v>
       </c>
       <c r="D16" s="69" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E16" s="68" t="s">
-        <v>211</v>
+        <v>332</v>
       </c>
       <c r="F16" s="77" t="s">
-        <v>206</v>
+        <v>150</v>
       </c>
       <c r="G16" s="63"/>
     </row>
@@ -6751,19 +7742,19 @@
         <v>17</v>
       </c>
       <c r="B17" s="64" t="s">
-        <v>168</v>
+        <v>293</v>
       </c>
       <c r="C17" s="65" t="s">
-        <v>204</v>
+        <v>327</v>
       </c>
       <c r="D17" s="66" t="s">
-        <v>202</v>
+        <v>325</v>
       </c>
       <c r="E17" s="64" t="s">
-        <v>212</v>
+        <v>333</v>
       </c>
       <c r="F17" s="77" t="s">
-        <v>208</v>
+        <v>330</v>
       </c>
       <c r="G17" s="61"/>
     </row>
@@ -6772,19 +7763,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="64" t="s">
-        <v>213</v>
+        <v>334</v>
       </c>
       <c r="C18" s="65" t="s">
-        <v>204</v>
+        <v>327</v>
       </c>
       <c r="D18" s="69" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E18" s="64" t="s">
-        <v>214</v>
+        <v>335</v>
       </c>
       <c r="F18" s="77" t="s">
-        <v>191</v>
+        <v>314</v>
       </c>
       <c r="G18" s="60"/>
     </row>
@@ -6793,19 +7784,19 @@
         <v>17</v>
       </c>
       <c r="B19" s="64" t="s">
-        <v>215</v>
+        <v>336</v>
       </c>
       <c r="C19" s="65" t="s">
-        <v>204</v>
+        <v>327</v>
       </c>
       <c r="D19" s="69" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E19" s="64" t="s">
-        <v>216</v>
+        <v>337</v>
       </c>
       <c r="F19" s="77" t="s">
-        <v>191</v>
+        <v>314</v>
       </c>
       <c r="G19" s="60"/>
     </row>
@@ -6814,16 +7805,16 @@
         <v>17</v>
       </c>
       <c r="B20" s="64" t="s">
-        <v>217</v>
+        <v>338</v>
       </c>
       <c r="C20" s="65" t="s">
-        <v>218</v>
+        <v>339</v>
       </c>
       <c r="D20" s="66" t="s">
-        <v>202</v>
+        <v>325</v>
       </c>
       <c r="E20" s="64" t="s">
-        <v>219</v>
+        <v>340</v>
       </c>
       <c r="F20" s="77"/>
       <c r="G20" s="60"/>
@@ -6833,16 +7824,16 @@
         <v>17</v>
       </c>
       <c r="B21" s="64" t="s">
-        <v>220</v>
+        <v>341</v>
       </c>
       <c r="C21" s="65" t="s">
-        <v>221</v>
+        <v>342</v>
       </c>
       <c r="D21" s="66" t="s">
-        <v>222</v>
+        <v>343</v>
       </c>
       <c r="E21" s="64" t="s">
-        <v>223</v>
+        <v>344</v>
       </c>
       <c r="F21" s="77"/>
       <c r="G21" s="60"/>
@@ -6852,16 +7843,16 @@
         <v>17</v>
       </c>
       <c r="B22" s="64" t="s">
-        <v>224</v>
+        <v>345</v>
       </c>
       <c r="C22" s="65" t="s">
-        <v>221</v>
+        <v>342</v>
       </c>
       <c r="D22" s="66" t="s">
-        <v>222</v>
+        <v>343</v>
       </c>
       <c r="E22" s="64" t="s">
-        <v>223</v>
+        <v>344</v>
       </c>
       <c r="F22" s="77"/>
       <c r="G22" s="60"/>
@@ -6871,19 +7862,19 @@
         <v>17</v>
       </c>
       <c r="B23" s="64" t="s">
-        <v>169</v>
+        <v>294</v>
       </c>
       <c r="C23" s="65" t="s">
-        <v>204</v>
+        <v>327</v>
       </c>
       <c r="D23" s="69" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E23" s="64" t="s">
-        <v>225</v>
+        <v>346</v>
       </c>
       <c r="F23" s="77" t="s">
-        <v>182</v>
+        <v>305</v>
       </c>
       <c r="G23" s="60"/>
     </row>
@@ -6892,19 +7883,19 @@
         <v>17</v>
       </c>
       <c r="B24" s="64" t="s">
-        <v>226</v>
+        <v>347</v>
       </c>
       <c r="C24" s="65" t="s">
-        <v>221</v>
+        <v>342</v>
       </c>
       <c r="D24" s="69" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E24" s="64" t="s">
-        <v>227</v>
+        <v>348</v>
       </c>
       <c r="F24" s="77" t="s">
-        <v>206</v>
+        <v>150</v>
       </c>
       <c r="G24" s="60"/>
     </row>
@@ -6913,19 +7904,19 @@
         <v>17</v>
       </c>
       <c r="B25" s="28" t="s">
-        <v>228</v>
+        <v>349</v>
       </c>
       <c r="C25" s="28" t="s">
-        <v>204</v>
+        <v>327</v>
       </c>
       <c r="D25" s="69" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E25" s="28" t="s">
-        <v>229</v>
+        <v>350</v>
       </c>
       <c r="F25" s="77" t="s">
-        <v>182</v>
+        <v>305</v>
       </c>
       <c r="G25" s="17"/>
     </row>
@@ -6934,19 +7925,19 @@
         <v>17</v>
       </c>
       <c r="B26" s="28" t="s">
-        <v>230</v>
+        <v>351</v>
       </c>
       <c r="C26" s="28" t="s">
-        <v>204</v>
+        <v>327</v>
       </c>
       <c r="D26" s="69" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E26" s="28" t="s">
-        <v>231</v>
+        <v>352</v>
       </c>
       <c r="F26" s="77" t="s">
-        <v>182</v>
+        <v>305</v>
       </c>
       <c r="G26" s="17"/>
     </row>
@@ -6959,1612 +7950,426 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CF1D022-2DCA-4C9F-85B3-06476B5333EE}">
-  <dimension ref="A1:F32"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A14F5E4-DCD2-4C2B-80EA-545272C1842A}">
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="18" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="72.5703125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" style="6" customWidth="1"/>
-    <col min="4" max="4" width="19.7109375" style="6" customWidth="1"/>
-    <col min="5" max="5" width="55.5703125" style="6" customWidth="1"/>
-    <col min="6" max="6" width="25" style="6" customWidth="1"/>
+    <col min="1" max="1" width="14.140625" customWidth="1"/>
+    <col min="2" max="2" width="52.5703125" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="105.5703125" customWidth="1"/>
+    <col min="5" max="5" width="42.42578125" customWidth="1"/>
+    <col min="6" max="7" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="31.5" customHeight="1">
-      <c r="A1" s="131" t="s">
-        <v>232</v>
-      </c>
-      <c r="B1" s="132"/>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="133"/>
-      <c r="F1"/>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="99" t="s">
+    <row r="1" spans="1:5" ht="25.7" customHeight="1">
+      <c r="A1" s="166" t="s">
+        <v>353</v>
+      </c>
+      <c r="B1" s="167"/>
+      <c r="C1" s="167"/>
+      <c r="D1" s="167"/>
+      <c r="E1" s="167"/>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="113" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="98" t="s">
+      <c r="B2" s="113" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="98" t="s">
+      <c r="C2" s="113" t="s">
         <v>50</v>
       </c>
-      <c r="D2" s="100" t="s">
+      <c r="D2" s="113" t="s">
         <v>51</v>
       </c>
-      <c r="E2" s="98" t="s">
+      <c r="E2" s="113" t="s">
         <v>52</v>
       </c>
-      <c r="F2"/>
-    </row>
-    <row r="3" spans="1:6" ht="264.75" customHeight="1">
-      <c r="A3" s="18">
+    </row>
+    <row r="3" spans="1:5" ht="290.10000000000002">
+      <c r="A3" s="3">
         <v>1</v>
       </c>
-      <c r="B3" s="95" t="s">
-        <v>233</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" s="96" t="s">
-        <v>234</v>
-      </c>
-      <c r="F3"/>
-    </row>
-    <row r="4" spans="1:6" ht="240" customHeight="1">
-      <c r="A4" s="20">
+      <c r="B3" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" s="3"/>
+    </row>
+    <row r="4" spans="1:5" ht="288.75" customHeight="1">
+      <c r="A4" s="2">
         <v>2</v>
       </c>
-      <c r="B4" s="95" t="s">
-        <v>235</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>180</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="E4" s="96" t="s">
-        <v>236</v>
-      </c>
-      <c r="F4"/>
-    </row>
-    <row r="5" spans="1:6" ht="159.6">
-      <c r="A5" s="20">
-        <v>3</v>
-      </c>
-      <c r="B5" s="95" t="s">
-        <v>237</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="E5" s="96" t="s">
-        <v>239</v>
-      </c>
-      <c r="F5"/>
-    </row>
-    <row r="6" spans="1:6" ht="186" customHeight="1">
-      <c r="A6" s="19">
-        <v>4</v>
-      </c>
-      <c r="B6" s="95" t="s">
-        <v>240</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>241</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="E6" s="96" t="s">
-        <v>242</v>
-      </c>
-      <c r="F6"/>
-    </row>
-    <row r="7" spans="1:6" ht="195.75" customHeight="1">
-      <c r="A7" s="19">
-        <v>5</v>
-      </c>
-      <c r="B7" s="95" t="s">
-        <v>243</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>244</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="E7" s="96" t="s">
-        <v>245</v>
-      </c>
-      <c r="F7"/>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="51" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="134" t="s">
-        <v>247</v>
-      </c>
-      <c r="B10" s="134"/>
-      <c r="C10" s="134"/>
-      <c r="D10" s="134"/>
-      <c r="E10" s="134"/>
-      <c r="F10" s="134"/>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="101" t="s">
+      <c r="B4" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A5" s="53"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="53"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="73" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="34.5" customHeight="1">
+      <c r="A7" s="168" t="s">
+        <v>360</v>
+      </c>
+      <c r="B7" s="169"/>
+      <c r="C7" s="169"/>
+      <c r="D7" s="169"/>
+      <c r="E7" s="169"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="114" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="102" t="s">
-        <v>166</v>
-      </c>
-      <c r="C11" s="102" t="s">
-        <v>63</v>
-      </c>
-      <c r="D11" s="103" t="s">
-        <v>248</v>
-      </c>
-      <c r="E11" s="102" t="s">
-        <v>65</v>
-      </c>
-      <c r="F11" s="102" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="17.25" customHeight="1">
-      <c r="A12" s="94" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="94" t="s">
-        <v>250</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>251</v>
-      </c>
-      <c r="D12" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="E12" s="22" t="s">
-        <v>252</v>
-      </c>
-      <c r="F12" s="93" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="94" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="94" t="s">
-        <v>101</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="D13" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="E13" s="22" t="s">
-        <v>255</v>
-      </c>
-      <c r="F13" s="93" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="94" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="94" t="s">
-        <v>256</v>
-      </c>
-      <c r="C14" s="97" t="s">
-        <v>152</v>
-      </c>
-      <c r="D14" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="E14" s="22" t="s">
-        <v>257</v>
-      </c>
-      <c r="F14" s="93" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="94" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="94" t="s">
-        <v>104</v>
-      </c>
-      <c r="C15" s="97" t="s">
-        <v>152</v>
-      </c>
-      <c r="D15" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="E15" s="22" t="s">
-        <v>258</v>
-      </c>
-      <c r="F15" s="93" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="94" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="94" t="s">
-        <v>108</v>
-      </c>
-      <c r="C16" s="97" t="s">
-        <v>152</v>
-      </c>
-      <c r="D16" s="25" t="s">
+      <c r="B8" s="113" t="s">
+        <v>361</v>
+      </c>
+      <c r="C8" s="115" t="s">
+        <v>137</v>
+      </c>
+      <c r="D8" s="113" t="s">
+        <v>362</v>
+      </c>
+      <c r="E8" s="116" t="s">
         <v>76</v>
       </c>
-      <c r="E16" s="22" t="s">
-        <v>259</v>
-      </c>
-      <c r="F16" s="93" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="94" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" s="94" t="s">
-        <v>110</v>
-      </c>
-      <c r="C17" s="97" t="s">
-        <v>152</v>
-      </c>
-      <c r="D17" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E17" s="26" t="s">
-        <v>261</v>
-      </c>
-      <c r="F17" s="93" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="94" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="94" t="s">
-        <v>132</v>
-      </c>
-      <c r="C18" s="97" t="s">
-        <v>152</v>
-      </c>
-      <c r="D18" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E18" s="26" t="s">
-        <v>262</v>
-      </c>
-      <c r="F18" s="93" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="94" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" s="94" t="s">
-        <v>112</v>
-      </c>
-      <c r="C19" s="97" t="s">
-        <v>152</v>
-      </c>
-      <c r="D19" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E19" s="26" t="s">
-        <v>263</v>
-      </c>
-      <c r="F19" s="93" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="94" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" s="94" t="s">
-        <v>116</v>
-      </c>
-      <c r="C20" s="24" t="s">
-        <v>265</v>
-      </c>
-      <c r="D20" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E20" s="22" t="s">
-        <v>266</v>
-      </c>
-      <c r="F20" s="93" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="94" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21" s="94" t="s">
-        <v>118</v>
-      </c>
-      <c r="C21" s="24" t="s">
-        <v>265</v>
-      </c>
-      <c r="D21" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E21" s="22" t="s">
-        <v>267</v>
-      </c>
-      <c r="F21" s="93" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" s="94" t="s">
-        <v>19</v>
-      </c>
-      <c r="B22" s="94" t="s">
-        <v>268</v>
-      </c>
-      <c r="C22" s="97" t="s">
-        <v>152</v>
-      </c>
-      <c r="D22" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E22" s="26" t="s">
-        <v>269</v>
-      </c>
-      <c r="F22" s="93" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" s="94" t="s">
-        <v>19</v>
-      </c>
-      <c r="B23" s="94" t="s">
-        <v>134</v>
-      </c>
-      <c r="C23" s="97" t="s">
-        <v>152</v>
-      </c>
-      <c r="D23" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E23" s="26" t="s">
-        <v>270</v>
-      </c>
-      <c r="F23" s="93" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" s="94" t="s">
-        <v>19</v>
-      </c>
-      <c r="B24" s="94" t="s">
-        <v>120</v>
-      </c>
-      <c r="C24" s="97" t="s">
-        <v>152</v>
-      </c>
-      <c r="D24" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E24" s="26" t="s">
-        <v>271</v>
-      </c>
-      <c r="F24" s="93" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" s="94" t="s">
-        <v>19</v>
-      </c>
-      <c r="B25" s="94" t="s">
-        <v>122</v>
-      </c>
-      <c r="C25" s="97" t="s">
-        <v>152</v>
-      </c>
-      <c r="D25" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E25" s="26" t="s">
-        <v>272</v>
-      </c>
-      <c r="F25" s="93" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26" s="94" t="s">
-        <v>19</v>
-      </c>
-      <c r="B26" s="94" t="s">
-        <v>124</v>
-      </c>
-      <c r="C26" s="97" t="s">
-        <v>152</v>
-      </c>
-      <c r="D26" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="E26" s="26" t="s">
-        <v>273</v>
-      </c>
-      <c r="F26" s="93" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="94" t="s">
-        <v>19</v>
-      </c>
-      <c r="B27" s="94" t="s">
-        <v>136</v>
-      </c>
-      <c r="C27" s="97" t="s">
-        <v>152</v>
-      </c>
-      <c r="D27" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E27" s="26" t="s">
-        <v>274</v>
-      </c>
-      <c r="F27" s="93" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" s="94" t="s">
-        <v>19</v>
-      </c>
-      <c r="B28" s="94" t="s">
-        <v>275</v>
-      </c>
-      <c r="C28" s="97" t="s">
-        <v>152</v>
-      </c>
-      <c r="D28" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E28" s="26" t="s">
-        <v>276</v>
-      </c>
-      <c r="F28" s="93" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="94" t="s">
-        <v>19</v>
-      </c>
-      <c r="B29" s="94" t="s">
-        <v>126</v>
-      </c>
-      <c r="C29" s="97" t="s">
-        <v>152</v>
-      </c>
-      <c r="D29" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E29" s="26" t="s">
-        <v>277</v>
-      </c>
-      <c r="F29" s="93" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" s="94" t="s">
-        <v>19</v>
-      </c>
-      <c r="B30" s="94" t="s">
-        <v>128</v>
-      </c>
-      <c r="C30" s="24" t="s">
-        <v>278</v>
-      </c>
-      <c r="D30" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E30" s="22" t="s">
-        <v>279</v>
-      </c>
-      <c r="F30" s="93" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" s="94" t="s">
-        <v>19</v>
-      </c>
-      <c r="B31" s="94" t="s">
-        <v>130</v>
-      </c>
-      <c r="C31" s="24" t="s">
-        <v>281</v>
-      </c>
-      <c r="D31" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E31" s="22" t="s">
-        <v>282</v>
-      </c>
-      <c r="F31" s="93" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="15"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="87" t="s">
+        <v>363</v>
+      </c>
+      <c r="B9" s="85" t="s">
+        <v>364</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="D9" s="86" t="s">
+        <v>365</v>
+      </c>
+      <c r="E9" s="88" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="101.45">
+      <c r="A10" s="87" t="s">
+        <v>363</v>
+      </c>
+      <c r="B10" s="85" t="s">
+        <v>367</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="D10" s="86" t="s">
+        <v>365</v>
+      </c>
+      <c r="E10" s="88" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="29.1">
+      <c r="A11" s="87" t="s">
+        <v>363</v>
+      </c>
+      <c r="B11" s="85" t="s">
+        <v>370</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D11" s="86" t="s">
+        <v>365</v>
+      </c>
+      <c r="E11" s="88" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="87" t="s">
+        <v>363</v>
+      </c>
+      <c r="B12" s="85" t="s">
+        <v>372</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D12" s="86" t="s">
+        <v>365</v>
+      </c>
+      <c r="E12" s="88" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="87" t="s">
+        <v>363</v>
+      </c>
+      <c r="B13" s="85" t="s">
+        <v>374</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="D13" s="86" t="s">
+        <v>365</v>
+      </c>
+      <c r="E13" s="88" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="43.5">
+      <c r="A14" s="87" t="s">
+        <v>363</v>
+      </c>
+      <c r="B14" s="85" t="s">
+        <v>377</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D14" s="86" t="s">
+        <v>365</v>
+      </c>
+      <c r="E14" s="88" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="37.5" customHeight="1">
+      <c r="A15" s="89" t="s">
+        <v>363</v>
+      </c>
+      <c r="B15" s="90" t="s">
+        <v>379</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="D15" s="91" t="s">
+        <v>365</v>
+      </c>
+      <c r="E15" s="92" t="s">
+        <v>380</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37797131-4575-41AC-AB4A-64D0D662358B}">
-  <dimension ref="A1:F54"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F46C07F1-1AE0-4A64-A0EA-5661CE7D091E}">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="63.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="68.5703125" customWidth="1"/>
-    <col min="6" max="6" width="32.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.140625" customWidth="1"/>
+    <col min="2" max="2" width="34.5703125" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="54" customWidth="1"/>
+    <col min="5" max="5" width="60.140625" customWidth="1"/>
+    <col min="6" max="7" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="135" t="s">
-        <v>283</v>
-      </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
-      <c r="E1" s="137"/>
-      <c r="F1" s="17"/>
-    </row>
-    <row r="2" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A2" s="107" t="s">
-        <v>284</v>
-      </c>
-      <c r="B2" s="107"/>
-      <c r="C2" s="107"/>
-      <c r="D2" s="107"/>
-      <c r="E2" s="107"/>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="108" t="s">
+    <row r="1" spans="1:5" ht="35.450000000000003" customHeight="1">
+      <c r="A1" s="166" t="s">
+        <v>381</v>
+      </c>
+      <c r="B1" s="167"/>
+      <c r="C1" s="167"/>
+      <c r="D1" s="167"/>
+      <c r="E1" s="167"/>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="113" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="106" t="s">
+      <c r="B2" s="115" t="s">
         <v>49</v>
       </c>
-      <c r="C3" s="106" t="s">
+      <c r="C2" s="115" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="109" t="s">
+      <c r="D2" s="113" t="s">
         <v>51</v>
       </c>
-      <c r="E3" s="106" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="29.1">
-      <c r="A4" s="9">
+      <c r="E2" s="113" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="67.349999999999994" customHeight="1">
+      <c r="A3" s="78">
         <v>1</v>
       </c>
-      <c r="B4" s="27" t="s">
-        <v>286</v>
-      </c>
-      <c r="C4" s="27" t="s">
-        <v>287</v>
-      </c>
-      <c r="D4" s="28" t="s">
-        <v>55</v>
-      </c>
-      <c r="E4" s="27" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="181.5" customHeight="1">
-      <c r="A5" s="9">
+      <c r="B3" s="54" t="s">
+        <v>382</v>
+      </c>
+      <c r="C3" s="54" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" s="79" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" s="55" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="64.7" customHeight="1">
+      <c r="A4" s="80">
         <v>2</v>
       </c>
-      <c r="B5" s="27" t="s">
-        <v>289</v>
-      </c>
-      <c r="C5" s="27" t="s">
-        <v>177</v>
-      </c>
-      <c r="D5" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="E5" s="27" t="s">
-        <v>290</v>
-      </c>
-      <c r="F5" s="17"/>
-    </row>
-    <row r="6" spans="1:6" ht="153" customHeight="1">
-      <c r="A6" s="9">
-        <v>3</v>
-      </c>
-      <c r="B6" s="27" t="s">
-        <v>291</v>
-      </c>
-      <c r="C6" s="27" t="s">
-        <v>292</v>
-      </c>
-      <c r="D6" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="E6" s="27" t="s">
-        <v>293</v>
-      </c>
-      <c r="F6" s="17"/>
-    </row>
-    <row r="7" spans="1:6" ht="215.25" customHeight="1">
-      <c r="A7" s="9">
-        <v>4</v>
-      </c>
-      <c r="B7" s="27" t="s">
-        <v>294</v>
-      </c>
-      <c r="C7" s="27" t="s">
-        <v>241</v>
-      </c>
-      <c r="D7" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="E7" s="27" t="s">
-        <v>295</v>
-      </c>
-      <c r="F7" s="17"/>
-    </row>
-    <row r="8" spans="1:6" ht="174" customHeight="1">
-      <c r="A8" s="9">
-        <v>5</v>
-      </c>
-      <c r="B8" s="27" t="s">
-        <v>296</v>
-      </c>
-      <c r="C8" s="27" t="s">
-        <v>297</v>
-      </c>
-      <c r="D8" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="E8" s="27" t="s">
-        <v>298</v>
-      </c>
-      <c r="F8" s="17"/>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="51" t="s">
-        <v>246</v>
-      </c>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="134" t="s">
-        <v>299</v>
-      </c>
-      <c r="B11" s="134"/>
-      <c r="C11" s="134"/>
-      <c r="D11" s="134"/>
-      <c r="E11" s="134"/>
-      <c r="F11" s="134"/>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="101" t="s">
+      <c r="B4" s="10" t="s">
+        <v>382</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D4" s="81" t="s">
+        <v>65</v>
+      </c>
+      <c r="E4" s="58" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15" customHeight="1">
+      <c r="A5" s="82"/>
+      <c r="B5" s="56"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="83"/>
+      <c r="E5" s="57"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="73" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15" customHeight="1" thickBot="1">
+      <c r="A7" s="166" t="s">
+        <v>386</v>
+      </c>
+      <c r="B7" s="167"/>
+      <c r="C7" s="167"/>
+      <c r="D7" s="167"/>
+      <c r="E7" s="167"/>
+    </row>
+    <row r="8" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A8" s="113" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="102" t="s">
-        <v>166</v>
-      </c>
-      <c r="C12" s="102" t="s">
-        <v>63</v>
-      </c>
-      <c r="D12" s="103" t="s">
-        <v>248</v>
-      </c>
-      <c r="E12" s="102" t="s">
-        <v>65</v>
-      </c>
-      <c r="F12" s="102" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" s="28" t="s">
-        <v>300</v>
-      </c>
-      <c r="C13" s="28" t="s">
-        <v>73</v>
-      </c>
-      <c r="D13" s="25" t="s">
+      <c r="B8" s="115" t="s">
+        <v>361</v>
+      </c>
+      <c r="C8" s="115" t="s">
+        <v>137</v>
+      </c>
+      <c r="D8" s="115" t="s">
+        <v>362</v>
+      </c>
+      <c r="E8" s="113" t="s">
         <v>76</v>
       </c>
-      <c r="E13" s="27" t="s">
-        <v>301</v>
-      </c>
-      <c r="F13" s="28" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="28" t="s">
-        <v>302</v>
-      </c>
-      <c r="C14" s="28" t="s">
-        <v>303</v>
-      </c>
-      <c r="D14" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E14" s="27" t="s">
-        <v>209</v>
-      </c>
-      <c r="F14" s="28" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" s="28" t="s">
-        <v>101</v>
-      </c>
-      <c r="C15" s="28" t="s">
-        <v>152</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="E15" s="28" t="s">
-        <v>304</v>
-      </c>
-      <c r="F15" s="28" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" s="28" t="s">
-        <v>305</v>
-      </c>
-      <c r="C16" s="28" t="s">
-        <v>152</v>
-      </c>
-      <c r="D16" s="29" t="s">
-        <v>76</v>
-      </c>
-      <c r="E16" s="28" t="s">
-        <v>306</v>
-      </c>
-      <c r="F16" s="28" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B17" s="28" t="s">
-        <v>308</v>
-      </c>
-      <c r="C17" s="28" t="s">
-        <v>152</v>
-      </c>
-      <c r="D17" s="29" t="s">
-        <v>76</v>
-      </c>
-      <c r="E17" s="28" t="s">
-        <v>309</v>
-      </c>
-      <c r="F17" s="28" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B18" s="28" t="s">
-        <v>310</v>
-      </c>
-      <c r="C18" s="28" t="s">
-        <v>152</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="E18" s="28" t="s">
-        <v>311</v>
-      </c>
-      <c r="F18" s="28" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19" s="28" t="s">
-        <v>312</v>
-      </c>
-      <c r="C19" s="28" t="s">
-        <v>152</v>
-      </c>
-      <c r="D19" s="29" t="s">
-        <v>76</v>
-      </c>
-      <c r="E19" s="28" t="s">
-        <v>313</v>
-      </c>
-      <c r="F19" s="28" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20" s="28" t="s">
-        <v>314</v>
-      </c>
-      <c r="C20" s="28" t="s">
-        <v>152</v>
-      </c>
-      <c r="D20" s="29" t="s">
-        <v>76</v>
-      </c>
-      <c r="E20" s="28" t="s">
-        <v>315</v>
-      </c>
-      <c r="F20" s="28" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B21" s="28" t="s">
-        <v>316</v>
-      </c>
-      <c r="C21" s="28" t="s">
-        <v>152</v>
-      </c>
-      <c r="D21" s="29" t="s">
-        <v>76</v>
-      </c>
-      <c r="E21" s="28" t="s">
-        <v>317</v>
-      </c>
-      <c r="F21" s="28" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B22" s="28" t="s">
-        <v>318</v>
-      </c>
-      <c r="C22" s="28" t="s">
-        <v>152</v>
-      </c>
-      <c r="D22" s="29" t="s">
-        <v>76</v>
-      </c>
-      <c r="E22" s="28" t="s">
-        <v>319</v>
-      </c>
-      <c r="F22" s="28" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" s="30" t="s">
-        <v>12</v>
-      </c>
-      <c r="B23" s="30" t="s">
-        <v>320</v>
-      </c>
-      <c r="C23" s="30" t="s">
-        <v>321</v>
-      </c>
-      <c r="D23" s="31" t="s">
-        <v>76</v>
-      </c>
-      <c r="E23" s="30" t="s">
-        <v>322</v>
-      </c>
-      <c r="F23" s="30" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B24" s="28" t="s">
-        <v>323</v>
-      </c>
-      <c r="C24" s="28" t="s">
-        <v>152</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="E24" s="28" t="s">
-        <v>324</v>
-      </c>
-      <c r="F24" s="28" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B25" s="28" t="s">
-        <v>325</v>
-      </c>
-      <c r="C25" s="28" t="s">
-        <v>152</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="E25" s="28" t="s">
-        <v>326</v>
-      </c>
-      <c r="F25" s="28" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="B26" s="32" t="s">
-        <v>327</v>
-      </c>
-      <c r="C26" s="28" t="s">
-        <v>152</v>
-      </c>
-      <c r="D26" s="33" t="s">
-        <v>76</v>
-      </c>
-      <c r="E26" s="32" t="s">
-        <v>328</v>
-      </c>
-      <c r="F26" s="32" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B27" s="28" t="s">
-        <v>329</v>
-      </c>
-      <c r="C27" s="28" t="s">
-        <v>152</v>
-      </c>
-      <c r="D27" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E27" s="28" t="s">
-        <v>330</v>
-      </c>
-      <c r="F27" s="28" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B28" s="28" t="s">
-        <v>331</v>
-      </c>
-      <c r="C28" s="28" t="s">
-        <v>152</v>
-      </c>
-      <c r="D28" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E28" s="28" t="s">
-        <v>332</v>
-      </c>
-      <c r="F28" s="28" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B29" s="28" t="s">
-        <v>334</v>
-      </c>
-      <c r="C29" s="28" t="s">
-        <v>152</v>
-      </c>
-      <c r="D29" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E29" s="28" t="s">
-        <v>335</v>
-      </c>
-      <c r="F29" s="28" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B30" s="28" t="s">
-        <v>336</v>
-      </c>
-      <c r="C30" s="28" t="s">
-        <v>152</v>
-      </c>
-      <c r="D30" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E30" s="28" t="s">
-        <v>337</v>
-      </c>
-      <c r="F30" s="28" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B31" s="28" t="s">
-        <v>338</v>
-      </c>
-      <c r="C31" s="28" t="s">
-        <v>152</v>
-      </c>
-      <c r="D31" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E31" s="28" t="s">
-        <v>339</v>
-      </c>
-      <c r="F31" s="28" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B32" s="28" t="s">
-        <v>340</v>
-      </c>
-      <c r="C32" s="28" t="s">
-        <v>152</v>
-      </c>
-      <c r="D32" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E32" s="28" t="s">
-        <v>341</v>
-      </c>
-      <c r="F32" s="28" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B33" s="28" t="s">
-        <v>342</v>
-      </c>
-      <c r="C33" s="28" t="s">
-        <v>152</v>
-      </c>
-      <c r="D33" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E33" s="28" t="s">
-        <v>343</v>
-      </c>
-      <c r="F33" s="28" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B34" s="28" t="s">
-        <v>344</v>
-      </c>
-      <c r="C34" s="28" t="s">
-        <v>152</v>
-      </c>
-      <c r="D34" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E34" s="28" t="s">
-        <v>345</v>
-      </c>
-      <c r="F34" s="28" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B35" s="28" t="s">
-        <v>346</v>
-      </c>
-      <c r="C35" s="28" t="s">
-        <v>152</v>
-      </c>
-      <c r="D35" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E35" s="28" t="s">
-        <v>347</v>
-      </c>
-      <c r="F35" s="28" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B36" s="28" t="s">
-        <v>348</v>
-      </c>
-      <c r="C36" s="28" t="s">
-        <v>152</v>
-      </c>
-      <c r="D36" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E36" s="28" t="s">
-        <v>349</v>
-      </c>
-      <c r="F36" s="28" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B37" s="28" t="s">
-        <v>350</v>
-      </c>
-      <c r="C37" s="28" t="s">
-        <v>152</v>
-      </c>
-      <c r="D37" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E37" s="28" t="s">
-        <v>351</v>
-      </c>
-      <c r="F37" s="28" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B38" s="28" t="s">
-        <v>352</v>
-      </c>
-      <c r="C38" s="28" t="s">
-        <v>152</v>
-      </c>
-      <c r="D38" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E38" s="28" t="s">
-        <v>353</v>
-      </c>
-      <c r="F38" s="28" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B39" s="28" t="s">
-        <v>354</v>
-      </c>
-      <c r="C39" s="28" t="s">
-        <v>152</v>
-      </c>
-      <c r="D39" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E39" s="28" t="s">
-        <v>355</v>
-      </c>
-      <c r="F39" s="28" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B40" s="28" t="s">
-        <v>356</v>
-      </c>
-      <c r="C40" s="28" t="s">
-        <v>357</v>
-      </c>
-      <c r="D40" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E40" s="28" t="s">
-        <v>358</v>
-      </c>
-      <c r="F40" s="28" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B41" s="28" t="s">
-        <v>360</v>
-      </c>
-      <c r="C41" s="28" t="s">
-        <v>357</v>
-      </c>
-      <c r="D41" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E41" s="28" t="s">
-        <v>361</v>
-      </c>
-      <c r="F41" s="28" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B42" s="28" t="s">
-        <v>362</v>
-      </c>
-      <c r="C42" s="28" t="s">
-        <v>152</v>
-      </c>
-      <c r="D42" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E42" s="28" t="s">
-        <v>363</v>
-      </c>
-      <c r="F42" s="28" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B43" s="28" t="s">
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="84" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="85" t="s">
+        <v>387</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="D9" s="86" t="s">
+        <v>365</v>
+      </c>
+      <c r="E9" s="84" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="84" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="85" t="s">
+        <v>389</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="D10" s="86" t="s">
+        <v>365</v>
+      </c>
+      <c r="E10" s="84" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="84" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="85" t="s">
         <v>364</v>
       </c>
-      <c r="C43" s="28" t="s">
-        <v>152</v>
-      </c>
-      <c r="D43" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E43" s="28" t="s">
+      <c r="C11" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="D11" s="86" t="s">
         <v>365</v>
       </c>
-      <c r="F43" s="28" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B44" s="28" t="s">
-        <v>367</v>
-      </c>
-      <c r="C44" s="28" t="s">
-        <v>152</v>
-      </c>
-      <c r="D44" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E44" s="28" t="s">
-        <v>368</v>
-      </c>
-      <c r="F44" s="28" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B45" s="28" t="s">
-        <v>369</v>
-      </c>
-      <c r="C45" s="28" t="s">
-        <v>152</v>
-      </c>
-      <c r="D45" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E45" s="28" t="s">
-        <v>370</v>
-      </c>
-      <c r="F45" s="28" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B46" s="28" t="s">
-        <v>371</v>
-      </c>
-      <c r="C46" s="28" t="s">
-        <v>152</v>
-      </c>
-      <c r="D46" s="34" t="s">
-        <v>113</v>
-      </c>
-      <c r="E46" s="28" t="s">
-        <v>372</v>
-      </c>
-      <c r="F46" s="28" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B47" s="28" t="s">
-        <v>374</v>
-      </c>
-      <c r="C47" s="28" t="s">
-        <v>357</v>
-      </c>
-      <c r="D47" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E47" s="28" t="s">
-        <v>375</v>
-      </c>
-      <c r="F47" s="28" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B48" s="28" t="s">
-        <v>376</v>
-      </c>
-      <c r="C48" s="28" t="s">
-        <v>152</v>
-      </c>
-      <c r="D48" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E48" s="28" t="s">
-        <v>377</v>
-      </c>
-      <c r="F48" s="28" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B49" s="28" t="s">
-        <v>378</v>
-      </c>
-      <c r="C49" s="28" t="s">
-        <v>152</v>
-      </c>
-      <c r="D49" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E49" s="28" t="s">
-        <v>379</v>
-      </c>
-      <c r="F49" s="28" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B50" s="28" t="s">
-        <v>380</v>
-      </c>
-      <c r="C50" s="28" t="s">
-        <v>381</v>
-      </c>
-      <c r="D50" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E50" s="28" t="s">
-        <v>382</v>
-      </c>
-      <c r="F50" s="28" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B51" s="28" t="s">
-        <v>384</v>
-      </c>
-      <c r="C51" s="28" t="s">
-        <v>152</v>
-      </c>
-      <c r="D51" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E51" s="28" t="s">
-        <v>385</v>
-      </c>
-      <c r="F51" s="28" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B52" s="28" t="s">
-        <v>386</v>
-      </c>
-      <c r="C52" s="28" t="s">
-        <v>152</v>
-      </c>
-      <c r="D52" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E52" s="28" t="s">
-        <v>387</v>
-      </c>
-      <c r="F52" s="28" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B53" s="28" t="s">
-        <v>388</v>
-      </c>
-      <c r="C53" s="28" t="s">
-        <v>152</v>
-      </c>
-      <c r="D53" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E53" s="27" t="s">
-        <v>389</v>
-      </c>
-      <c r="F53" s="28" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B54" s="28" t="s">
-        <v>390</v>
-      </c>
-      <c r="C54" s="28" t="s">
+      <c r="E11" s="84" t="s">
         <v>391</v>
       </c>
-      <c r="D54" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E54" s="27" t="s">
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="84" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="85" t="s">
         <v>392</v>
       </c>
-      <c r="F54" s="28" t="s">
+      <c r="C12" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E12" s="84" t="s">
         <v>393</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
